--- a/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>A</t>
   </si>
@@ -656,397 +656,421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1658000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1688000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1672000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1717000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1756000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1849000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1718000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1607000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1674000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1660000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1586000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1525000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1548000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1483000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1261000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1238000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1357000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1367000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1274000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1238000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1284000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1294000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1203000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1206000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1211000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1189000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1114000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1102000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1111000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>773000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1014000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>793000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>788000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>837000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>779000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>746000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>764000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>760000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>734000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>708000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>710000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>695000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>592000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>583000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>634000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>628000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>581000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>569000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>572000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>576000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>545000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>558000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>538000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>540000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>519000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>511000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>494000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>908000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>915000</v>
+      </c>
+      <c r="F10" s="3">
         <v>658000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>924000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>968000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1012000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>939000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>861000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>910000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>900000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>852000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>817000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>838000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>788000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>669000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>655000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>723000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>739000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>693000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>669000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>712000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>718000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>658000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>648000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>673000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>649000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>595000</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>591000</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>573000</v>
       </c>
       <c r="AE10" s="3">
         <v>591000</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>573000</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>591000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1078,97 +1102,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>114000</v>
+      </c>
+      <c r="F12" s="3">
         <v>102000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>111000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>97000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>119000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>116000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>115000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>117000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>116000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>113000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>109000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>103000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>102000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>92000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>197000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>104000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>102000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>101000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>99000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>102000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>104000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>97000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>92000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>93000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>89000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>87000</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>84000</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>79000</v>
       </c>
       <c r="AE12" s="3">
         <v>84000</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3">
+        <v>79000</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1256,19 +1288,25 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>9000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -1294,23 +1332,23 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>4000</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
@@ -1318,20 +1356,20 @@
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y14" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>-15000</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
@@ -1345,8 +1383,14 @@
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1434,8 +1478,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1464,186 +1514,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1274000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1539000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1334000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1330000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1378000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1307000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1247000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1298000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1265000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1250000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1237000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1220000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1184000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1031000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1136000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1142000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1117000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1049000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1022000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1034000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1035000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>982000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>996000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>972000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>956000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>913000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>901000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>861000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>928000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>408000</v>
+      </c>
+      <c r="F18" s="3">
         <v>133000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>383000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>426000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>471000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>411000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>360000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>376000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>395000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>336000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>288000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>328000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>299000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>230000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>102000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>215000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>250000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>225000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>216000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>250000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>259000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>221000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>210000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>239000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>233000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>201000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>201000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>206000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1675,209 +1739,223 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F20" s="3">
         <v>23000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>18000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>9000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>7000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>5000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-36000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>74000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>12000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>8000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>39000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>24000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>15000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>19000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>16000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>3000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>39000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>36000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>14000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>13000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>11000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>10000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>504000</v>
+      </c>
+      <c r="F21" s="3">
         <v>227000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>472000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>502000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>551000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>496000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>436000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>422000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>553000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>432000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>370000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>407000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>378000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>315000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>217000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>318000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>328000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>295000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>288000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>320000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>318000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>313000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>296000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>304000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>298000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>263000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>265000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>268000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>226000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F22" s="3">
         <v>24000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>24000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>25000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>23000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>19000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>21000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>21000</v>
       </c>
       <c r="K22" s="3">
         <v>21000</v>
@@ -1886,242 +1964,260 @@
         <v>21000</v>
       </c>
       <c r="M22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="N22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="O22" s="3">
         <v>20000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>19000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>19000</v>
       </c>
       <c r="P22" s="3">
         <v>19000</v>
       </c>
       <c r="Q22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="R22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="S22" s="3">
         <v>20000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>20000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>21000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>18000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>17000</v>
       </c>
       <c r="V22" s="3">
         <v>18000</v>
       </c>
       <c r="W22" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="X22" s="3">
         <v>18000</v>
       </c>
       <c r="Y22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>19000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>20000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>20000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>19000</v>
       </c>
       <c r="AC22" s="3">
         <v>20000</v>
       </c>
       <c r="AD22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>20000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>420000</v>
+      </c>
+      <c r="F23" s="3">
         <v>132000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>377000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>410000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>455000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>397000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>333000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>319000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>448000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>327000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>273000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>312000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>283000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>219000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>121000</v>
       </c>
       <c r="R23" s="3">
         <v>219000</v>
       </c>
       <c r="S23" s="3">
+        <v>121000</v>
+      </c>
+      <c r="T23" s="3">
+        <v>219000</v>
+      </c>
+      <c r="U23" s="3">
         <v>231000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>222000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>218000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>248000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>244000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>242000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>227000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>233000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>226000</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>193000</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>191000</v>
       </c>
       <c r="AD23" s="3">
         <v>193000</v>
       </c>
       <c r="AE23" s="3">
+        <v>191000</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AG23" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="F24" s="3">
         <v>21000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>75000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>58000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>87000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>68000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>59000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>36000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>6000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>63000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>57000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>24000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>61000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>20000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>20000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>22000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>37000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>31000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>36000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-256000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>30000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>6000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>22000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>20000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>49000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>18000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>27000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>25000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2209,186 +2305,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>348000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>475000</v>
+      </c>
+      <c r="F26" s="3">
         <v>111000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>302000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>352000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>368000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>329000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>274000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>283000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>442000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>264000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>216000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>288000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>222000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>199000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>101000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>197000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>194000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>191000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>182000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>504000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>214000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>236000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>205000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>213000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>177000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>175000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>164000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>168000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>348000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>475000</v>
+      </c>
+      <c r="F27" s="3">
         <v>111000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>302000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>352000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>368000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>329000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>274000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>283000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>442000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>264000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>216000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>288000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>222000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>199000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>101000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>197000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>194000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>191000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>182000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>504000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>214000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>236000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>205000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>213000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>177000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>175000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>164000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>168000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2476,8 +2590,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2520,11 +2640,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>10</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>10</v>
@@ -2538,35 +2658,41 @@
       <c r="V29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W29" s="3">
-        <v>-19000</v>
+      <c r="W29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Y29" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-533000</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2654,8 +2780,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2743,186 +2875,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-23000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-18000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-9000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-7000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-5000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>36000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-74000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-12000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-39000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-24000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-15000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-19000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-16000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-3000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-39000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>348000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>475000</v>
+      </c>
+      <c r="F33" s="3">
         <v>111000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>302000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>352000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>368000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>329000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>274000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>283000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>442000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>264000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>216000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>288000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>222000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>199000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>101000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>197000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>194000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>191000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>182000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>504000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>195000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>236000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>205000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-320000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>177000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>175000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>164000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>168000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3010,191 +3160,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>348000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>475000</v>
+      </c>
+      <c r="F35" s="3">
         <v>111000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>302000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>352000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>368000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>329000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>274000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>283000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>442000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>264000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>216000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>288000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>222000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>199000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>101000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>197000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>194000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>191000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>182000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>504000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>195000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>236000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>205000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-320000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>177000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>175000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>164000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>168000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3226,8 +3394,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3259,97 +3429,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1748000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1590000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1329000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1175000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1250000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1053000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1071000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1186000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1113000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1484000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1428000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1380000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1329000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1441000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1358000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1324000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1226000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1382000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1765000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2155000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2057000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2247000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2131000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3011000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2887000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2678000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2389000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3362,26 +3540,26 @@
       <c r="F42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="G42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>6000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>21000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>45000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>91000</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>10</v>
@@ -3392,11 +3570,11 @@
       <c r="P42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3437,631 +3615,679 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1295000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1291000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1339000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1401000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1459000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1405000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1345000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1237000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1205000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1172000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1122000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1075000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1087000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1038000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>930000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>886000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>966000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>930000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>856000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>819000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>833000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>776000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>733000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>754000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>751000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>724000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>678000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>677000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>653000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1033000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1031000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1072000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1103000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1111000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1038000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1010000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>937000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>879000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>830000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>818000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>791000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>755000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>720000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>746000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>750000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>706000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>679000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>660000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>657000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>653000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>638000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>623000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>594000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>608000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>575000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>566000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>548000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>551000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>533000</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>274000</v>
+      </c>
+      <c r="F45" s="3">
         <v>290000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>270000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>258000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>282000</v>
       </c>
       <c r="H45" s="3">
         <v>258000</v>
       </c>
       <c r="I45" s="3">
+        <v>282000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>258000</v>
+      </c>
+      <c r="K45" s="3">
         <v>262000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>232000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>222000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>264000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>268000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>312000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>216000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>211000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>211000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>204000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>198000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>176000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>181000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>169000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>187000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>180000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>166000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>151000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>192000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>189000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>186000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>190000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>182000</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4338000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4186000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4030000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3949000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4078000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3778000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3690000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3643000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3474000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3799000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3632000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3514000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3483000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3415000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3245000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3171000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3102000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3189000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3457000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3812000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3712000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3848000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3667000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4525000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>4397000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4169000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3996000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3800000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3635000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3635000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>164000</v>
+      </c>
+      <c r="F47" s="3">
         <v>190000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>186000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>188000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>195000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>194000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>190000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>191000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>185000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>204000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>188000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>165000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>158000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>148000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>141000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>118000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>102000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>99000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>96000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>77000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>68000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>70000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>139000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>140000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>138000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>137000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>134000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>133000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1469000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1424000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1377000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1338000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1147000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1250000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1212000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1172000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1144000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1123000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1087000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1070000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1039000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1020000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1029000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1024000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1035000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>850000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>839000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>827000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>829000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>822000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>801000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>798000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>792000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>757000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>716000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>675000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>653000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4410000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4435000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4486000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4778000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4793000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4773000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4797000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4854000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4893000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4956000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>5008000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>5059000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4405000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4433000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4482000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4503000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>4648000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4700000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3618000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3650000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3699000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3464000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3448000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2932000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2968000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2987000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>2933000</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4149,8 +4375,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4238,97 +4470,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>554000</v>
+      </c>
+      <c r="F52" s="3">
         <v>592000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>541000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>713000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>536000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>591000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>596000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>625000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>642000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>560000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>567000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>582000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>601000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>642000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>616000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>598000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>611000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>612000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>637000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>635000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>339000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>363000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>390000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>395000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>394000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>425000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>466000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>477000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4416,97 +4660,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10948000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10763000</v>
+      </c>
+      <c r="F54" s="3">
         <v>10675000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10792000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10919000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10532000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10484000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10455000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10327000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10705000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10491000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10398000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9674000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>9627000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>9546000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>9455000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>9501000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>9452000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>8625000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>9022000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>8952000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>8541000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>8349000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>8784000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>8698000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>8426000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>8261000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>8016000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>7872000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>7794000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4538,8 +4794,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4571,542 +4829,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>418000</v>
+      </c>
+      <c r="F57" s="3">
         <v>452000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>479000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>540000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>580000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>558000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>503000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>475000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>446000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>416000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>423000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>398000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>354000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>311000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>333000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>329000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>354000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>316000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>314000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>315000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>340000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>273000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>271000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>292000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>305000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>289000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>265000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>268000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>55000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>238000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>36000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>180000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>175000</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="L58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>130000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>205000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>314000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>75000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>40000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>700000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>675000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>616000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>504000</v>
       </c>
-      <c r="U58" s="3" t="s">
+      <c r="W58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V58" s="3" t="s">
+      <c r="X58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>315000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>345000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>210000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>280000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>241000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>190000</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1185000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1253000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1187000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1158000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1245000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1164000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1135000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1109000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1262000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1178000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1130000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>975000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1038000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>963000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>912000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>888000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1110000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>802000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>804000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>780000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>831000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>741000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>779000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>724000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>748000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>672000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>681000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>631000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>688000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1617000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1603000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1760000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1666000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1936000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1861000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1902000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1813000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1584000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1708000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1724000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1758000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1687000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1467000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1314000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1945000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1892000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2080000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1622000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1118000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1095000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1171000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1014000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1365000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1361000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1263000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1241000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1187000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1089000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2555000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2735000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2734000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>2733000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>2733000</v>
       </c>
       <c r="G61" s="3">
         <v>2733000</v>
       </c>
       <c r="H61" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="J61" s="3">
         <v>2732000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2730000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2730000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2729000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2728000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2727000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2185000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2284000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2283000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1788000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1787000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1791000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1294000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1798000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1798000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1799000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1799000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1800000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1800000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1801000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1801000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1802000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1802000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>588000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>580000</v>
+      </c>
+      <c r="F62" s="3">
         <v>623000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>612000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>641000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>633000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>759000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>790000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>859000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>879000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1093000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1103000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>998000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1003000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>968000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>954000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>974000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>833000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>962000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>981000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1023000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1000000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>968000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1002000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1011000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>527000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>608000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>652000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>681000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5194,8 +5490,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5283,8 +5585,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5372,97 +5680,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4760000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="F66" s="3">
         <v>5117000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5011000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5310000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5227000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5393000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5333000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5173000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5316000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5545000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5588000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4870000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4754000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4565000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4687000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4653000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4704000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3878000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3897000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3916000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3974000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3785000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4171000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>4176000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3595000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>3653000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>3644000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>3575000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>3551000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5494,8 +5814,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5583,8 +5905,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5672,8 +6000,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5761,8 +6095,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5850,97 +6190,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1061000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>782000</v>
+      </c>
+      <c r="F72" s="3">
         <v>444000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>700000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>541000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>324000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>139000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>160000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>159000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>348000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>90000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-12000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>81000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>130000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>15000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>73000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-18000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-122000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>178000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>90000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-336000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-416000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-412000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-529000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-126000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-393000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>6089000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6028,8 +6380,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6117,8 +6475,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6206,97 +6570,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6188000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5845000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5558000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5781000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5609000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5305000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5091000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5122000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5154000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5389000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4946000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4810000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4804000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4873000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4981000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4768000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4848000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4748000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4747000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5125000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5036000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4567000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4564000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4613000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4522000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4831000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4608000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4372000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4297000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4243000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6384,191 +6760,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>348000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>475000</v>
+      </c>
+      <c r="F81" s="3">
         <v>111000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>302000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>352000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>368000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>329000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>274000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>283000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>442000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>264000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>216000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>288000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>222000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>199000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>101000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>197000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>194000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>191000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>182000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>504000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>195000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>236000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>205000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-320000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>177000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>175000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>164000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>168000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6600,97 +6994,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>62000</v>
+      </c>
+      <c r="F83" s="3">
         <v>71000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>71000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>67000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>73000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>80000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>82000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>82000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>84000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>84000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>77000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>76000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>76000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>77000</v>
       </c>
       <c r="Q83" s="3">
         <v>76000</v>
       </c>
       <c r="R83" s="3">
-        <v>79000</v>
+        <v>77000</v>
       </c>
       <c r="S83" s="3">
         <v>76000</v>
       </c>
       <c r="T83" s="3">
+        <v>79000</v>
+      </c>
+      <c r="U83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="V83" s="3">
         <v>55000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>53000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>54000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>56000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>53000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>50000</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>51000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>52000</v>
       </c>
       <c r="AB83" s="3">
         <v>51000</v>
       </c>
       <c r="AC83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>51000</v>
+      </c>
+      <c r="AE83" s="3">
         <v>54000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>55000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6778,8 +7180,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6867,8 +7275,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6956,8 +7370,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7045,8 +7465,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7134,97 +7560,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>485000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>516000</v>
+      </c>
+      <c r="F89" s="3">
         <v>562000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>398000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>296000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>448000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>326000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>283000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>255000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>441000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>334000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>472000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>238000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>377000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>290000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>313000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-59000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>314000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>242000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>252000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>213000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>372000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>197000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>303000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>215000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>288000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>228000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>257000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>116000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7256,97 +7694,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-81000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-57000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-76000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-70000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-82000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-64000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-75000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-62000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-55000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-31000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-41000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-27000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-33000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-34000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-30000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-47000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-39000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-39000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-36000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-48000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7434,8 +7880,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7523,97 +7975,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-89000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-77000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-104000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-110000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-73000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-76000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-79000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-59000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-61000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-587000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-42000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-27000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-53000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-35000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-51000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-56000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-290000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-114000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-473000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-60000</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-101000</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-43000</v>
       </c>
       <c r="AD94" s="3">
         <v>-101000</v>
       </c>
       <c r="AE94" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-78000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7645,37 +8109,39 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-66000</v>
+        <v>-69000</v>
       </c>
       <c r="E96" s="3">
         <v>-66000</v>
       </c>
       <c r="F96" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="G96" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-67000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-62000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-62000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-63000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-63000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-59000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-59000</v>
       </c>
       <c r="M96" s="3">
         <v>-59000</v>
@@ -7684,10 +8150,10 @@
         <v>-59000</v>
       </c>
       <c r="O96" s="3">
-        <v>-55000</v>
+        <v>-59000</v>
       </c>
       <c r="P96" s="3">
-        <v>-56000</v>
+        <v>-59000</v>
       </c>
       <c r="Q96" s="3">
         <v>-55000</v>
@@ -7696,34 +8162,34 @@
         <v>-56000</v>
       </c>
       <c r="S96" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="T96" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-51000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-51000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-52000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-52000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-48000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-48000</v>
       </c>
       <c r="Z96" s="3">
         <v>-48000</v>
       </c>
       <c r="AA96" s="3">
-        <v>-43000</v>
+        <v>-48000</v>
       </c>
       <c r="AB96" s="3">
-        <v>-42000</v>
+        <v>-48000</v>
       </c>
       <c r="AC96" s="3">
         <v>-43000</v>
@@ -7732,10 +8198,16 @@
         <v>-42000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7823,8 +8295,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7912,8 +8390,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8001,271 +8485,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-240000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-322000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-390000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-17000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-341000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-362000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-123000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-546000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-324000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-222000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>166000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-316000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-269000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-231000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-156000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-61000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>497000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-582000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-92000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-122000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-131000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-589000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-114000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>37000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>29000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-56000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>22000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-14000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>9000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-11000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>24000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>18000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>261000</v>
+      </c>
+      <c r="F102" s="3">
         <v>154000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-75000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>197000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-17000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-115000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>72000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-374000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>55000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>48000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>51000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-111000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>83000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>35000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>97000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-156000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-383000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-390000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>97000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-190000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>116000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-880000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>124000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>209000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>115000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>174000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>148000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>90000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>A</t>
   </si>
@@ -656,421 +656,433 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1573000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1658000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1688000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1672000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1717000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1756000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1849000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1718000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1607000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1674000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1660000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1586000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1525000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1483000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1261000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1238000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1357000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1367000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1274000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1238000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1284000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1294000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1203000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1206000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1211000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1189000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1114000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1102000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1111000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>717000</v>
+      </c>
+      <c r="E9" s="3">
         <v>750000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>773000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1014000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>793000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>788000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>837000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>779000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>746000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>764000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>760000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>734000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>708000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>710000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>695000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>592000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>583000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>634000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>628000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>581000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>569000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>572000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>576000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>545000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>558000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>538000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>540000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>519000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>511000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>494000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>856000</v>
+      </c>
+      <c r="E10" s="3">
         <v>908000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>915000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>658000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>924000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>968000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1012000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>939000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>861000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>910000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>900000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>852000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>817000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>838000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>788000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>669000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>655000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>723000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>739000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>693000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>669000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>712000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>718000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>658000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>648000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>673000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>649000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>595000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>591000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>573000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1104,103 +1116,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E12" s="3">
         <v>126000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>114000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>102000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>111000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>97000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>119000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>116000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>115000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>117000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>116000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>113000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>109000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>103000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>102000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>92000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>197000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>104000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>102000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>101000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>99000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>102000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>104000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>97000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>92000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>93000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>89000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>87000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>84000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>79000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1294,22 +1310,25 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>9000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
@@ -1338,20 +1357,20 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>3000</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>3000</v>
       </c>
       <c r="S14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4000</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
@@ -1362,17 +1381,17 @@
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-15000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
@@ -1389,8 +1408,11 @@
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1484,8 +1506,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1516,198 +1541,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1210000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1274000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1280000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1539000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1334000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1330000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1378000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1307000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1247000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1298000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1265000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1250000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1237000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1184000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1031000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1136000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1142000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1117000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1049000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1022000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1034000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1035000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>982000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>996000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>972000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>956000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>913000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>901000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>861000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>928000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>363000</v>
+      </c>
+      <c r="E18" s="3">
         <v>384000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>408000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>133000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>383000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>426000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>471000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>411000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>360000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>376000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>395000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>336000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>288000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>328000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>299000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>230000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>102000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>215000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>250000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>225000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>216000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>250000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>259000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>221000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>210000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>239000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>233000</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>201000</v>
       </c>
       <c r="AE18" s="3">
         <v>201000</v>
       </c>
       <c r="AF18" s="3">
+        <v>201000</v>
+      </c>
+      <c r="AG18" s="3">
         <v>206000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1741,224 +1773,231 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E20" s="3">
         <v>41000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>34000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>23000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>18000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-36000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>74000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>3000</v>
       </c>
       <c r="Q20" s="3">
         <v>3000</v>
       </c>
       <c r="R20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>39000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>24000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>15000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>19000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>16000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>39000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>36000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>14000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>13000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>11000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>457000</v>
+      </c>
+      <c r="E21" s="3">
         <v>487000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>504000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>227000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>472000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>502000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>551000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>496000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>436000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>422000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>553000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>432000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>370000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>407000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>378000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>315000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>217000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>318000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>328000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>295000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>288000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>320000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>318000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>313000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>296000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>304000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>298000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>263000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>265000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>268000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>226000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="E22" s="3">
         <v>22000</v>
       </c>
       <c r="F22" s="3">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="G22" s="3">
         <v>24000</v>
       </c>
       <c r="H22" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I22" s="3">
         <v>25000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>21000</v>
       </c>
       <c r="L22" s="3">
         <v>21000</v>
@@ -1970,10 +2009,10 @@
         <v>21000</v>
       </c>
       <c r="O22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="P22" s="3">
         <v>20000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>19000</v>
       </c>
       <c r="Q22" s="3">
         <v>19000</v>
@@ -1982,22 +2021,22 @@
         <v>19000</v>
       </c>
       <c r="S22" s="3">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="T22" s="3">
         <v>20000</v>
       </c>
       <c r="U22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="V22" s="3">
         <v>21000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>18000</v>
       </c>
       <c r="Y22" s="3">
         <v>18000</v>
@@ -2006,218 +2045,227 @@
         <v>18000</v>
       </c>
       <c r="AA22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>20000</v>
       </c>
       <c r="AC22" s="3">
         <v>20000</v>
       </c>
       <c r="AD22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>20000</v>
       </c>
       <c r="AF22" s="3">
         <v>20000</v>
       </c>
       <c r="AG22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E23" s="3">
         <v>403000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>420000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>132000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>377000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>410000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>455000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>397000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>333000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>319000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>448000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>327000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>273000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>312000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>283000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>219000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>121000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>219000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>231000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>222000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>218000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>248000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>244000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>242000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>227000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>233000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>226000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>193000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>191000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>193000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E24" s="3">
         <v>55000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-55000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>75000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>58000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>87000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>68000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>59000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>63000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>57000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>61000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>20000</v>
       </c>
       <c r="S24" s="3">
         <v>20000</v>
       </c>
       <c r="T24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="U24" s="3">
         <v>22000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>36000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-256000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>30000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>22000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>20000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>49000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>18000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>27000</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>25000</v>
       </c>
       <c r="AG24" s="3">
         <v>25000</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2311,198 +2359,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E26" s="3">
         <v>348000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>475000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>111000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>302000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>352000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>368000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>329000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>274000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>283000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>442000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>264000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>216000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>288000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>222000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>199000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>101000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>197000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>194000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>191000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>182000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>504000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>214000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>236000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>205000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>213000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>177000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>175000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>164000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>168000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E27" s="3">
         <v>348000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>475000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>111000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>302000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>352000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>368000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>329000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>274000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>283000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>442000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>264000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>216000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>288000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>222000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>199000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>101000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>197000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>194000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>191000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>182000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>504000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>214000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>236000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>205000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>213000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>177000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>175000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>164000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>168000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2596,8 +2653,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2646,8 +2706,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>10</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>10</v>
@@ -2664,23 +2724,23 @@
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-19000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-533000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
@@ -2688,11 +2748,14 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2786,8 +2849,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2881,198 +2947,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-41000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-34000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-23000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-18000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>36000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-74000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-3000</v>
       </c>
       <c r="Q32" s="3">
         <v>-3000</v>
       </c>
       <c r="R32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-39000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-24000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-15000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-19000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E33" s="3">
         <v>348000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>475000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>111000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>302000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>352000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>368000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>329000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>274000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>283000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>442000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>264000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>216000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>288000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>222000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>199000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>101000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>197000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>194000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>191000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>182000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>504000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>195000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>236000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>205000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-320000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>177000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>175000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>164000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>168000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3166,203 +3241,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E35" s="3">
         <v>348000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>475000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>111000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>302000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>352000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>368000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>329000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>274000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>283000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>442000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>264000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>216000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>288000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>222000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>199000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>101000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>197000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>194000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>191000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>182000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>504000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>195000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>236000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>205000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-320000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>177000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>175000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>164000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>168000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3396,8 +3480,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3431,103 +3516,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1671000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1748000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1590000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1329000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1175000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1250000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1053000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1071000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1186000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1113000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1484000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1428000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1380000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1329000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1441000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1358000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1324000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1226000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1382000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1765000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2155000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2057000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2247000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2131000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3011000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2887000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2678000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2389000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3546,23 +3635,23 @@
       <c r="H42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
+      <c r="I42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>6000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>45000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>91000</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>10</v>
@@ -3576,8 +3665,8 @@
       <c r="R42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3621,673 +3710,697 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1249000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1295000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1291000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1339000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1401000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1459000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1405000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1345000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1237000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1205000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1172000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1122000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1075000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1087000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1038000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>930000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>886000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>966000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>930000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>856000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>819000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>833000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>776000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>733000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>754000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>751000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>724000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>678000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>677000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>653000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1033000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1031000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1072000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1103000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1111000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1038000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1010000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>937000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>879000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>830000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>818000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>791000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>755000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>720000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>746000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>750000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>706000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>679000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>660000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>657000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>653000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>638000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>623000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>594000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>608000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>575000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>566000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>548000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>551000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>533000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E45" s="3">
         <v>262000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>274000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>290000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>270000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>258000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>282000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>258000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>262000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>232000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>222000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>264000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>268000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>312000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>216000</v>
-      </c>
-      <c r="R45" s="3">
-        <v>211000</v>
       </c>
       <c r="S45" s="3">
         <v>211000</v>
       </c>
       <c r="T45" s="3">
+        <v>211000</v>
+      </c>
+      <c r="U45" s="3">
         <v>204000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>198000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>176000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>181000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>169000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>187000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>180000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>166000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>151000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>192000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>189000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>186000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>190000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>182000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4203000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4338000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4186000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4030000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3949000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4078000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3778000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3690000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3643000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3474000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3799000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3632000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3514000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3483000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3415000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3245000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3171000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3102000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3189000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3457000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3812000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3712000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3848000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3667000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4525000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4397000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4169000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3996000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3800000</v>
-      </c>
-      <c r="AF46" s="3">
-        <v>3635000</v>
       </c>
       <c r="AG46" s="3">
         <v>3635000</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>3635000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E47" s="3">
         <v>170000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>164000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>190000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>186000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>188000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>195000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>194000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>190000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>191000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>185000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>204000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>188000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>165000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>158000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>148000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>141000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>118000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>102000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>99000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>96000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>77000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>68000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>70000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>139000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>140000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>138000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>137000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>134000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>133000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1533000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1469000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1424000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1377000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1338000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1147000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1250000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1212000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1172000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1144000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1123000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1087000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1070000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1039000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1020000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1029000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1024000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1035000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>850000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>839000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>827000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>829000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>822000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>801000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>798000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>792000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>757000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>716000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>675000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>653000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4380000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4410000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4435000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4486000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4778000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4793000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4773000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4797000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4854000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4893000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4956000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5008000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5059000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4405000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4433000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4482000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4503000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4648000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4700000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3618000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3650000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3699000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3464000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3448000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2932000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2968000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2987000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2933000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4381,8 +4494,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4476,103 +4592,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>563000</v>
+      </c>
+      <c r="E52" s="3">
         <v>561000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>554000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>592000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>541000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>713000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>536000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>591000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>596000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>625000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>642000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>560000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>567000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>582000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>601000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>642000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>616000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>598000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>611000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>612000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>637000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>635000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>339000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>363000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>390000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>395000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>394000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>425000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>466000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>477000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4666,103 +4788,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10856000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10948000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10763000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10675000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10792000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10919000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10532000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10484000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10455000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10327000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10705000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10491000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10398000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9674000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9627000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9546000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9455000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9501000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9452000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8625000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9022000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8952000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8541000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8349000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8784000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8698000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8426000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8261000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8016000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7872000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7794000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4796,8 +4924,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4831,402 +4960,415 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>461000</v>
+      </c>
+      <c r="E57" s="3">
         <v>488000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>418000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>452000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>479000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>540000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>580000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>558000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>503000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>475000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>446000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>416000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>423000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>398000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>354000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>311000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>333000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>329000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>354000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>316000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>314000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>315000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>340000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>273000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>271000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>292000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>305000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>289000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>265000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>268000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>55000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>238000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>36000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>180000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>175000</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>130000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>205000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>314000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>75000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>40000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>675000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>616000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>504000</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>315000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>345000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>210000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>280000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>241000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>190000</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1077000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1129000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1185000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1253000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1187000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1158000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1245000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1164000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1135000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1109000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1262000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1178000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1130000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>975000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1038000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>963000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>912000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>888000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1110000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>802000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>804000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>780000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>831000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>741000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>779000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>724000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>748000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>672000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>681000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>631000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>688000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1958000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1617000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1603000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1760000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1666000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1936000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1861000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1902000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1813000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1584000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1708000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1724000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1758000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1687000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1467000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1314000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1945000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1892000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2080000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1622000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1118000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1095000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1171000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1014000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1361000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1263000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1241000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1187000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1089000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2136000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2555000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2735000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2734000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>2733000</v>
       </c>
       <c r="H61" s="3">
         <v>2733000</v>
@@ -5235,174 +5377,180 @@
         <v>2733000</v>
       </c>
       <c r="J61" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="K61" s="3">
         <v>2732000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2730000</v>
       </c>
       <c r="L61" s="3">
         <v>2730000</v>
       </c>
       <c r="M61" s="3">
+        <v>2730000</v>
+      </c>
+      <c r="N61" s="3">
         <v>2729000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2728000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2727000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2185000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2284000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2283000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1788000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1787000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1791000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1294000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>1798000</v>
       </c>
       <c r="X61" s="3">
         <v>1798000</v>
       </c>
       <c r="Y61" s="3">
-        <v>1799000</v>
+        <v>1798000</v>
       </c>
       <c r="Z61" s="3">
         <v>1799000</v>
       </c>
       <c r="AA61" s="3">
-        <v>1800000</v>
+        <v>1799000</v>
       </c>
       <c r="AB61" s="3">
         <v>1800000</v>
       </c>
       <c r="AC61" s="3">
-        <v>1801000</v>
+        <v>1800000</v>
       </c>
       <c r="AD61" s="3">
         <v>1801000</v>
       </c>
       <c r="AE61" s="3">
-        <v>1802000</v>
+        <v>1801000</v>
       </c>
       <c r="AF61" s="3">
         <v>1802000</v>
       </c>
       <c r="AG61" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>548000</v>
+      </c>
+      <c r="E62" s="3">
         <v>588000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>580000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>623000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>612000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>641000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>633000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>759000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>790000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>859000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>879000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1093000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1103000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>998000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1003000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>968000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>954000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>974000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>833000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>962000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>981000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1023000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1000000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>968000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1002000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1011000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>527000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>608000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>652000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>681000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5496,8 +5644,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5591,8 +5742,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5686,103 +5840,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4642000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4760000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4918000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5117000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5011000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5310000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5227000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5393000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5333000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5173000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5316000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5545000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5588000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4870000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4754000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4565000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4687000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4653000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4704000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3878000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3897000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3916000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3974000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3785000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4171000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4176000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3595000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3653000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3644000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3575000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3551000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5816,8 +5976,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5911,8 +6072,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6006,8 +6170,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6101,8 +6268,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6196,103 +6366,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1090000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1061000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>782000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>444000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>700000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>541000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>324000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>139000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>160000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>159000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>348000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>90000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>81000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>130000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>73000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-18000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-122000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>178000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>90000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-336000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-416000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-412000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-529000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-126000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-393000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6089000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6386,8 +6562,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6481,8 +6660,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6576,103 +6758,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6214000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6188000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5845000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5558000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5781000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5609000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5305000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5091000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5122000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5154000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5389000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4946000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4810000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4804000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4873000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4981000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4768000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4848000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4748000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4747000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5125000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5036000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4567000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4564000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4613000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4522000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4831000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4608000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4372000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4297000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4243000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6766,203 +6954,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E81" s="3">
         <v>348000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>475000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>111000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>302000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>352000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>368000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>329000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>274000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>283000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>442000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>264000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>216000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>288000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>222000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>199000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>101000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>197000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>194000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>191000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>182000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>504000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>195000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>236000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>205000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-320000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>177000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>175000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>164000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>168000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6996,103 +7193,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="E83" s="3">
         <v>62000</v>
       </c>
       <c r="F83" s="3">
-        <v>71000</v>
+        <v>62000</v>
       </c>
       <c r="G83" s="3">
         <v>71000</v>
       </c>
       <c r="H83" s="3">
+        <v>71000</v>
+      </c>
+      <c r="I83" s="3">
         <v>67000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>73000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>80000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>82000</v>
       </c>
       <c r="L83" s="3">
         <v>82000</v>
       </c>
       <c r="M83" s="3">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="N83" s="3">
         <v>84000</v>
       </c>
       <c r="O83" s="3">
+        <v>84000</v>
+      </c>
+      <c r="P83" s="3">
         <v>77000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>76000</v>
       </c>
       <c r="Q83" s="3">
         <v>76000</v>
       </c>
       <c r="R83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="S83" s="3">
         <v>77000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>76000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>79000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>76000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>55000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>53000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>54000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>56000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>53000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>51000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>52000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>51000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>54000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>55000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7186,8 +7387,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7281,8 +7485,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7376,8 +7583,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7471,8 +7681,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7566,103 +7779,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E89" s="3">
         <v>485000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>516000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>562000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>398000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>296000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>448000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>326000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>283000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>255000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>441000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>334000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>472000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>238000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>377000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>290000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>313000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-59000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>314000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>242000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>252000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>213000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>372000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>197000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>303000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>215000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>288000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>228000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>257000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>116000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7696,103 +7915,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-90000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-84000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-81000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-57000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-76000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-70000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-82000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-64000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-75000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-62000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-33000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-34000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-30000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-39000</v>
       </c>
       <c r="X91" s="3">
         <v>-39000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58000</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-43000</v>
       </c>
       <c r="AE91" s="3">
         <v>-43000</v>
       </c>
       <c r="AF91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7886,8 +8109,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7981,103 +8207,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-95000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-40000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-89000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-104000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-110000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-73000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-76000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-79000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-59000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-61000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-587000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-32000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-53000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-51000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-56000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-290000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-114000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-473000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-78000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8111,8 +8343,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8120,7 +8353,7 @@
         <v>-69000</v>
       </c>
       <c r="E96" s="3">
-        <v>-66000</v>
+        <v>-69000</v>
       </c>
       <c r="F96" s="3">
         <v>-66000</v>
@@ -8129,22 +8362,22 @@
         <v>-66000</v>
       </c>
       <c r="H96" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-67000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-62000</v>
       </c>
       <c r="J96" s="3">
         <v>-62000</v>
       </c>
       <c r="K96" s="3">
-        <v>-63000</v>
+        <v>-62000</v>
       </c>
       <c r="L96" s="3">
         <v>-63000</v>
       </c>
       <c r="M96" s="3">
-        <v>-59000</v>
+        <v>-63000</v>
       </c>
       <c r="N96" s="3">
         <v>-59000</v>
@@ -8156,34 +8389,34 @@
         <v>-59000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-55000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-56000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-55000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-56000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-51000</v>
       </c>
       <c r="V96" s="3">
         <v>-51000</v>
       </c>
       <c r="W96" s="3">
-        <v>-52000</v>
+        <v>-51000</v>
       </c>
       <c r="X96" s="3">
         <v>-52000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-48000</v>
       </c>
       <c r="AA96" s="3">
         <v>-48000</v>
@@ -8192,22 +8425,25 @@
         <v>-48000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8301,8 +8537,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8396,8 +8635,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8491,289 +8733,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-291000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-240000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-201000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-322000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-390000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-341000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-362000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-123000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-546000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-324000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-222000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>166000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-316000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-269000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-231000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-156000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-61000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>497000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-582000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-92000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-122000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-131000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-589000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>37000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>29000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-56000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E101" s="3">
         <v>7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-3000</v>
       </c>
       <c r="N101" s="3">
         <v>-3000</v>
       </c>
       <c r="O101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>9000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>8000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-1000</v>
       </c>
       <c r="U101" s="3">
         <v>-1000</v>
       </c>
       <c r="V101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>9000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-11000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-15000</v>
       </c>
       <c r="AA101" s="3">
         <v>-15000</v>
       </c>
       <c r="AB101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AC101" s="3">
         <v>24000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>18000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E102" s="3">
         <v>157000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>261000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>154000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-75000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>197000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-115000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>72000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-374000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>55000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>51000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-111000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>83000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>35000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>97000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-156000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-383000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-390000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>97000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-190000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>116000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-880000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>124000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>209000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>115000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>174000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>148000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>90000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>A</t>
   </si>
@@ -656,433 +656,445 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1578000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1573000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1658000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1688000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1672000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1717000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1756000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1849000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1718000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1607000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1674000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1660000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1586000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1525000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1548000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1483000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1261000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1238000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1357000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1367000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1274000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1238000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1284000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1294000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1203000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1206000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1211000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1189000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1114000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1102000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1111000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>711000</v>
+      </c>
+      <c r="E9" s="3">
         <v>717000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>750000</v>
       </c>
-      <c r="F9" s="3">
-        <v>773000</v>
-      </c>
       <c r="G9" s="3">
+        <v>762000</v>
+      </c>
+      <c r="H9" s="3">
         <v>1014000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>793000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>788000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>837000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>779000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>746000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>764000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>760000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>734000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>708000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>710000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>695000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>592000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>583000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>634000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>628000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>581000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>569000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>572000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>576000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>545000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>558000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>538000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>540000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>519000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>511000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>494000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E10" s="3">
         <v>856000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>908000</v>
       </c>
-      <c r="F10" s="3">
-        <v>915000</v>
-      </c>
       <c r="G10" s="3">
+        <v>926000</v>
+      </c>
+      <c r="H10" s="3">
         <v>658000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>924000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>968000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1012000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>939000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>861000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>910000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>900000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>852000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>817000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>838000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>788000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>669000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>655000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>723000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>739000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>693000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>669000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>712000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>718000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>658000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>648000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>673000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>649000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>595000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>591000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>573000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1117,106 +1129,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E12" s="3">
         <v>113000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>126000</v>
       </c>
-      <c r="F12" s="3">
-        <v>114000</v>
-      </c>
       <c r="G12" s="3">
+        <v>108000</v>
+      </c>
+      <c r="H12" s="3">
         <v>102000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>111000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>97000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>119000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>116000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>115000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>117000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>116000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>113000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>109000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>103000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>102000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>92000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>197000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>104000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>102000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>101000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>99000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>102000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>104000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>97000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>92000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>93000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>89000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>87000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>84000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>79000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,25 +1329,28 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H14" s="3">
         <v>9000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>10</v>
@@ -1360,20 +1379,20 @@
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>3000</v>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>3000</v>
       </c>
       <c r="T14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="U14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
@@ -1384,17 +1403,17 @@
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-15000</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
@@ -1411,8 +1430,11 @@
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1509,8 +1531,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1542,204 +1567,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1245000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1210000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1274000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1280000</v>
-      </c>
       <c r="G17" s="3">
+        <v>1237000</v>
+      </c>
+      <c r="H17" s="3">
         <v>1539000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1334000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1330000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1378000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1307000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1247000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1298000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1265000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1250000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1237000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1220000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1184000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1031000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1136000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1142000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1117000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1049000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1022000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1034000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1035000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>982000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>996000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>972000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>956000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>913000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>901000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>861000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>928000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E18" s="3">
         <v>363000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>384000</v>
       </c>
-      <c r="F18" s="3">
-        <v>408000</v>
-      </c>
       <c r="G18" s="3">
+        <v>451000</v>
+      </c>
+      <c r="H18" s="3">
         <v>133000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>383000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>426000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>471000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>411000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>360000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>376000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>395000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>336000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>288000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>328000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>299000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>230000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>102000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>215000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>250000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>225000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>216000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>250000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>259000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>221000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>210000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>239000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>233000</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>201000</v>
       </c>
       <c r="AF18" s="3">
         <v>201000</v>
       </c>
       <c r="AG18" s="3">
+        <v>201000</v>
+      </c>
+      <c r="AH18" s="3">
         <v>206000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1774,233 +1806,240 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E20" s="3">
         <v>31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>41000</v>
       </c>
-      <c r="F20" s="3">
-        <v>34000</v>
-      </c>
       <c r="G20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="H20" s="3">
         <v>23000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>18000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-36000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>74000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>3000</v>
       </c>
       <c r="R20" s="3">
         <v>3000</v>
       </c>
       <c r="S20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T20" s="3">
         <v>8000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>39000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>24000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>15000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>19000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>16000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>39000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>36000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>14000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>13000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>7000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E21" s="3">
         <v>457000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>487000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>504000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>227000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>472000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>502000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>551000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>496000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>436000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>422000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>553000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>432000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>370000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>407000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>378000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>315000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>217000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>318000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>328000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>295000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>288000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>320000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>318000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>313000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>296000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>304000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>298000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>263000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>265000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>268000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>226000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E22" s="3">
         <v>20000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>22000</v>
       </c>
       <c r="F22" s="3">
         <v>22000</v>
       </c>
       <c r="G22" s="3">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="H22" s="3">
         <v>24000</v>
       </c>
       <c r="I22" s="3">
+        <v>24000</v>
+      </c>
+      <c r="J22" s="3">
         <v>25000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>23000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>21000</v>
       </c>
       <c r="M22" s="3">
         <v>21000</v>
@@ -2012,10 +2051,10 @@
         <v>21000</v>
       </c>
       <c r="P22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>20000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>19000</v>
       </c>
       <c r="R22" s="3">
         <v>19000</v>
@@ -2024,22 +2063,22 @@
         <v>19000</v>
       </c>
       <c r="T22" s="3">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="U22" s="3">
         <v>20000</v>
       </c>
       <c r="V22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="W22" s="3">
         <v>21000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>18000</v>
       </c>
       <c r="Z22" s="3">
         <v>18000</v>
@@ -2048,224 +2087,233 @@
         <v>18000</v>
       </c>
       <c r="AB22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>20000</v>
       </c>
       <c r="AD22" s="3">
         <v>20000</v>
       </c>
       <c r="AE22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>20000</v>
       </c>
       <c r="AG22" s="3">
         <v>20000</v>
       </c>
       <c r="AH22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E23" s="3">
         <v>374000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>403000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>420000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>132000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>377000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>410000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>455000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>397000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>333000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>319000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>448000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>327000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>273000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>312000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>283000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>219000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>121000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>219000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>231000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>222000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>218000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>248000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>244000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>242000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>227000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>233000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>226000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>193000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>191000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>193000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E24" s="3">
         <v>66000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>55000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-55000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>75000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>58000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>87000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>68000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>59000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>36000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>63000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>57000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>61000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>20000</v>
       </c>
       <c r="T24" s="3">
         <v>20000</v>
       </c>
       <c r="U24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="V24" s="3">
         <v>22000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>37000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>36000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-256000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>30000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>22000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>20000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>49000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>18000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>27000</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>25000</v>
       </c>
       <c r="AH24" s="3">
         <v>25000</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2362,204 +2410,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E26" s="3">
         <v>308000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>348000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>475000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>111000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>302000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>352000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>368000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>329000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>274000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>283000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>442000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>264000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>216000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>288000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>222000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>199000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>101000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>197000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>194000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>191000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>182000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>504000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>214000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>236000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>205000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>213000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>177000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>175000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>164000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>168000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E27" s="3">
         <v>308000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>348000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>475000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>111000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>302000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>352000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>368000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>329000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>274000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>283000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>442000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>264000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>216000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>288000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>222000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>199000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>101000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>197000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>194000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>191000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>182000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>504000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>214000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>236000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>205000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>213000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>177000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>175000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>164000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>168000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2656,8 +2713,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2709,8 +2769,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>10</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>10</v>
@@ -2727,23 +2787,23 @@
       <c r="Y29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-19000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-533000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
@@ -2751,11 +2811,14 @@
       <c r="AG29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2852,8 +2915,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2950,204 +3016,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-41000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-34000</v>
-      </c>
       <c r="G32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-23000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-18000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>36000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-74000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-3000</v>
       </c>
       <c r="R32" s="3">
         <v>-3000</v>
       </c>
       <c r="S32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="T32" s="3">
         <v>-8000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-39000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-24000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-15000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E33" s="3">
         <v>308000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>348000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>475000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>111000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>302000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>352000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>368000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>329000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>274000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>283000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>442000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>264000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>216000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>288000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>222000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>199000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>101000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>197000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>194000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>191000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>182000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>504000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>195000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>236000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>205000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-320000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>177000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>175000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>164000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>168000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3244,209 +3319,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E35" s="3">
         <v>308000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>348000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>475000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>111000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>302000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>352000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>368000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>329000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>274000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>283000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>442000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>264000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>216000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>288000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>222000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>199000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>101000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>197000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>194000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>191000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>182000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>504000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>195000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>236000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>205000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-320000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>177000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>175000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>164000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>168000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3481,8 +3565,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3517,144 +3602,148 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1779000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1671000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1748000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1590000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1329000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1175000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1250000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1053000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1071000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1186000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1113000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1484000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1428000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1380000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1329000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1441000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1358000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1324000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1226000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1382000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1765000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2155000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2057000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2247000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2131000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3011000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2887000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2678000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2389000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>10</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>6000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>45000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>91000</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>10</v>
@@ -3668,8 +3757,8 @@
       <c r="S42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3713,694 +3802,718 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1249000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1295000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1291000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1339000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1401000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1459000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1405000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1345000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1237000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1205000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1172000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1122000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1075000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1087000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1038000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>930000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>886000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>966000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>930000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>856000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>819000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>833000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>776000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>733000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>754000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>751000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>724000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>678000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>677000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>653000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>978000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1000000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1033000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1031000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1072000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1103000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1111000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1038000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1010000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>937000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>879000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>830000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>818000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>791000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>755000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>720000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>746000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>750000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>706000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>679000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>660000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>657000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>653000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>638000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>623000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>594000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>608000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>575000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>566000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>548000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>551000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>533000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E45" s="3">
         <v>283000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>262000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>274000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>290000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>270000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>258000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>282000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>258000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>262000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>232000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>222000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>264000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>268000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>312000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>216000</v>
-      </c>
-      <c r="S45" s="3">
-        <v>211000</v>
       </c>
       <c r="T45" s="3">
         <v>211000</v>
       </c>
       <c r="U45" s="3">
+        <v>211000</v>
+      </c>
+      <c r="V45" s="3">
         <v>204000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>198000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>176000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>181000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>169000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>187000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>180000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>166000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>151000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>192000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>189000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>186000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>190000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>182000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4256000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4203000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4338000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4186000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4030000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3949000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4078000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3778000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3690000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3643000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3474000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3799000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3632000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3514000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3483000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3415000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3245000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3171000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3102000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3189000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3457000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3812000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3712000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3848000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3667000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4525000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4397000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4169000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3996000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3800000</v>
-      </c>
-      <c r="AG46" s="3">
-        <v>3635000</v>
       </c>
       <c r="AH46" s="3">
         <v>3635000</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>3635000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>186000</v>
+      </c>
+      <c r="E47" s="3">
         <v>177000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>170000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>164000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>190000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>186000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>188000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>195000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>194000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>190000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>191000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>185000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>204000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>188000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>165000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>158000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>148000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>141000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>118000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>102000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>99000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>96000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>77000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>68000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>70000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>139000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>140000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>138000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>137000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>134000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>133000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1533000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1469000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1424000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1377000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1338000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1147000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1250000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1212000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1172000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1144000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1123000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1087000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1070000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1039000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1020000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1029000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1024000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1035000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>850000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>839000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>827000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>829000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>822000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>801000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>798000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>792000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>757000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>716000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>675000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>653000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4357000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4380000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4410000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4435000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4486000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4778000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4793000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4773000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4797000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4854000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4893000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4956000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5008000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5059000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4405000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4433000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4482000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4503000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4648000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4700000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3618000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3650000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3699000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3464000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3448000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2932000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2968000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2987000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2933000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4497,8 +4610,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4595,106 +4711,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E52" s="3">
         <v>563000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>561000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>554000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>592000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>541000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>713000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>536000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>591000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>596000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>625000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>642000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>560000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>567000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>582000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>601000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>642000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>616000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>598000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>611000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>612000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>637000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>635000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>339000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>363000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>390000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>395000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>394000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>425000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>466000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>477000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4791,106 +4913,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10996000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10856000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10948000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10763000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10675000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10792000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10919000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10532000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10484000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10455000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10327000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10705000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10491000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10398000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9674000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9627000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9546000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9455000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9501000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9452000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8625000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9022000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8952000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8541000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8349000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8784000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8698000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8426000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8261000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8016000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7872000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7794000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4925,8 +5053,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4961,417 +5090,430 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>497000</v>
+      </c>
+      <c r="E57" s="3">
         <v>461000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>488000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>418000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>452000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>479000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>540000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>580000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>558000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>503000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>475000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>446000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>416000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>423000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>398000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>354000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>311000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>333000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>329000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>354000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>316000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>314000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>315000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>340000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>273000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>271000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>292000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>305000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>289000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>265000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>268000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>795000</v>
+      </c>
+      <c r="E58" s="3">
         <v>420000</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>55000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>238000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>36000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>180000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>175000</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="N58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>130000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>205000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>314000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>75000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>40000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>700000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>675000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>616000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>504000</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>315000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>345000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>210000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>280000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>241000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>190000</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1097000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1077000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1129000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1185000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1253000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1187000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1158000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1245000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1164000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1135000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1109000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1262000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1178000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1130000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>975000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1038000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>963000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>912000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>888000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1110000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>802000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>804000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>780000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>831000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>741000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>779000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>724000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>748000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>672000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>681000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>631000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>688000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2389000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1958000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1617000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1603000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1760000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1666000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1936000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1861000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1902000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1813000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1584000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1708000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1724000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1758000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1687000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1467000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1314000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1945000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1892000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2080000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1622000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1118000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1095000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1171000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1014000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1361000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1263000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1241000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1187000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1089000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2137000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2136000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2555000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2735000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2734000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2733000</v>
       </c>
       <c r="I61" s="3">
         <v>2733000</v>
@@ -5380,177 +5522,183 @@
         <v>2733000</v>
       </c>
       <c r="K61" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="L61" s="3">
         <v>2732000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2730000</v>
       </c>
       <c r="M61" s="3">
         <v>2730000</v>
       </c>
       <c r="N61" s="3">
+        <v>2730000</v>
+      </c>
+      <c r="O61" s="3">
         <v>2729000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2728000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2727000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2185000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2284000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2283000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1788000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1787000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1791000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1294000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>1798000</v>
       </c>
       <c r="Y61" s="3">
         <v>1798000</v>
       </c>
       <c r="Z61" s="3">
-        <v>1799000</v>
+        <v>1798000</v>
       </c>
       <c r="AA61" s="3">
         <v>1799000</v>
       </c>
       <c r="AB61" s="3">
-        <v>1800000</v>
+        <v>1799000</v>
       </c>
       <c r="AC61" s="3">
         <v>1800000</v>
       </c>
       <c r="AD61" s="3">
-        <v>1801000</v>
+        <v>1800000</v>
       </c>
       <c r="AE61" s="3">
         <v>1801000</v>
       </c>
       <c r="AF61" s="3">
-        <v>1802000</v>
+        <v>1801000</v>
       </c>
       <c r="AG61" s="3">
         <v>1802000</v>
       </c>
       <c r="AH61" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E62" s="3">
         <v>548000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>588000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>580000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>623000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>612000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>641000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>633000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>759000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>790000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>859000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>879000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1093000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1103000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>998000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1003000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>968000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>954000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>974000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>833000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>962000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>981000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1023000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1000000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>968000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1002000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1011000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>527000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>608000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>652000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>681000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5647,8 +5795,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5745,8 +5896,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5843,106 +5997,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5093000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4642000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4760000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4918000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5117000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5011000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5310000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5227000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5393000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5333000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5173000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5316000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5545000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5588000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4870000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4754000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4565000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4687000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4653000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4704000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3878000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3897000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3916000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3974000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3785000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4171000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4176000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3595000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3653000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3644000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3575000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3551000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5977,8 +6137,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6075,8 +6236,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6173,8 +6337,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6271,8 +6438,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6369,106 +6539,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>773000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1090000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1061000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>782000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>444000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>700000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>541000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>324000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>139000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>160000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>159000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>348000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>90000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>81000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>130000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>73000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-122000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>178000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>90000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-336000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-416000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-412000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-529000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-126000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-393000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6089000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6565,8 +6741,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6663,8 +6842,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6761,106 +6943,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5903000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6214000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6188000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5845000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5558000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5781000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5609000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5305000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5091000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5122000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5154000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5389000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4946000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4810000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4804000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4873000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4981000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4768000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4848000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4748000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4747000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5125000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5036000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4567000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4564000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4613000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4522000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4831000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4608000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4372000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4297000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4243000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6957,209 +7145,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E81" s="3">
         <v>308000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>348000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>475000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>111000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>302000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>352000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>368000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>329000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>274000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>283000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>442000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>264000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>216000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>288000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>222000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>199000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>101000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>197000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>194000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>191000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>182000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>504000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>195000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>236000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>205000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-320000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>177000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>175000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>164000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>168000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7194,8 +7391,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7203,97 +7401,100 @@
         <v>63000</v>
       </c>
       <c r="E83" s="3">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="F83" s="3">
         <v>62000</v>
       </c>
       <c r="G83" s="3">
-        <v>71000</v>
+        <v>62000</v>
       </c>
       <c r="H83" s="3">
         <v>71000</v>
       </c>
       <c r="I83" s="3">
+        <v>71000</v>
+      </c>
+      <c r="J83" s="3">
         <v>67000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>73000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>80000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>82000</v>
       </c>
       <c r="M83" s="3">
         <v>82000</v>
       </c>
       <c r="N83" s="3">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="O83" s="3">
         <v>84000</v>
       </c>
       <c r="P83" s="3">
+        <v>84000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>77000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>76000</v>
       </c>
       <c r="R83" s="3">
         <v>76000</v>
       </c>
       <c r="S83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="T83" s="3">
         <v>77000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>76000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>79000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>76000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>55000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>53000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>54000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>56000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>53000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>52000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>51000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>54000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>55000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7390,8 +7591,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7488,8 +7692,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7586,8 +7793,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7684,8 +7894,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7782,106 +7995,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>452000</v>
+      </c>
+      <c r="E89" s="3">
         <v>333000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>485000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>516000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>562000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>398000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>296000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>448000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>326000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>283000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>255000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>441000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>334000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>472000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>238000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>377000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>290000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>313000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-59000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>314000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>242000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>252000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>213000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>372000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>197000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>303000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>215000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>288000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>228000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>257000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>116000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7916,106 +8135,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-103000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-90000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-84000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-76000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-70000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-82000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-64000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-75000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-62000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-55000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-33000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-34000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-30000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-39000</v>
       </c>
       <c r="Y91" s="3">
         <v>-39000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-58000</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-43000</v>
       </c>
       <c r="AF91" s="3">
         <v>-43000</v>
       </c>
       <c r="AG91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8112,8 +8335,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8210,106 +8436,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-109000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-95000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-40000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-89000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-104000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-110000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-73000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-76000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-79000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-61000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-587000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-42000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-32000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-53000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-51000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-290000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-473000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-78000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8344,19 +8576,20 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-69000</v>
+        <v>-68000</v>
       </c>
       <c r="E96" s="3">
         <v>-69000</v>
       </c>
       <c r="F96" s="3">
-        <v>-66000</v>
+        <v>-69000</v>
       </c>
       <c r="G96" s="3">
         <v>-66000</v>
@@ -8365,22 +8598,22 @@
         <v>-66000</v>
       </c>
       <c r="I96" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-67000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-62000</v>
       </c>
       <c r="K96" s="3">
         <v>-62000</v>
       </c>
       <c r="L96" s="3">
-        <v>-63000</v>
+        <v>-62000</v>
       </c>
       <c r="M96" s="3">
         <v>-63000</v>
       </c>
       <c r="N96" s="3">
-        <v>-59000</v>
+        <v>-63000</v>
       </c>
       <c r="O96" s="3">
         <v>-59000</v>
@@ -8392,34 +8625,34 @@
         <v>-59000</v>
       </c>
       <c r="R96" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-55000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-56000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-55000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-56000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-51000</v>
       </c>
       <c r="W96" s="3">
         <v>-51000</v>
       </c>
       <c r="X96" s="3">
-        <v>-52000</v>
+        <v>-51000</v>
       </c>
       <c r="Y96" s="3">
         <v>-52000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-48000</v>
       </c>
       <c r="AB96" s="3">
         <v>-48000</v>
@@ -8428,22 +8661,25 @@
         <v>-48000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8540,8 +8776,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8638,8 +8877,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8736,298 +8978,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-291000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-240000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-201000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-322000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-390000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-341000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-362000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-123000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-546000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-324000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-222000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>166000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-316000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-269000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-231000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-156000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-61000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>497000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-582000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-92000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-122000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-131000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-589000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>37000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>29000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-56000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-14000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>22000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-3000</v>
       </c>
       <c r="O101" s="3">
         <v>-3000</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>9000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-1000</v>
       </c>
       <c r="V101" s="3">
         <v>-1000</v>
       </c>
       <c r="W101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>9000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-15000</v>
       </c>
       <c r="AB101" s="3">
         <v>-15000</v>
       </c>
       <c r="AC101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AD101" s="3">
         <v>24000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>18000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-76000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>157000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>261000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>154000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-75000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>197000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-115000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>72000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-374000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>55000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>48000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>51000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-111000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>83000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>35000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>97000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-156000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-383000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-390000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>97000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-190000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>116000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-880000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>124000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>209000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>115000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>174000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>148000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>90000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>A</t>
   </si>
@@ -656,445 +656,457 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1701000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1578000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1573000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1658000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1688000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1672000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1717000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1756000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1849000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1718000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1607000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1674000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1660000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1586000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1525000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1548000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1483000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1261000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1238000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1357000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1367000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1274000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1238000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1284000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1294000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1203000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1206000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1211000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1189000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1114000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1102000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1111000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>711000</v>
+        <v>785000</v>
       </c>
       <c r="E9" s="3">
+        <v>723000</v>
+      </c>
+      <c r="F9" s="3">
         <v>717000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>750000</v>
       </c>
-      <c r="G9" s="3">
-        <v>762000</v>
-      </c>
       <c r="H9" s="3">
+        <v>773000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1014000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>793000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>788000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>837000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>779000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>746000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>764000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>760000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>734000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>708000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>710000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>695000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>592000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>583000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>634000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>628000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>581000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>569000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>572000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>576000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>545000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>558000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>538000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>540000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>519000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>511000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>494000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>867000</v>
+        <v>916000</v>
       </c>
       <c r="E10" s="3">
+        <v>855000</v>
+      </c>
+      <c r="F10" s="3">
         <v>856000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>908000</v>
       </c>
-      <c r="G10" s="3">
-        <v>926000</v>
-      </c>
       <c r="H10" s="3">
+        <v>915000</v>
+      </c>
+      <c r="I10" s="3">
         <v>658000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>924000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>968000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1012000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>939000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>861000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>910000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>900000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>852000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>817000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>838000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>788000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>669000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>655000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>723000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>739000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>693000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>669000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>712000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>718000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>658000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>648000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>673000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>649000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>595000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>591000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>573000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1130,109 +1142,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E12" s="3">
         <v>109000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>113000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
+        <v>120000</v>
+      </c>
+      <c r="H12" s="3">
+        <v>114000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>118000</v>
+      </c>
+      <c r="J12" s="3">
         <v>126000</v>
       </c>
-      <c r="G12" s="3">
-        <v>108000</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="K12" s="3">
+        <v>97000</v>
+      </c>
+      <c r="L12" s="3">
+        <v>119000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>116000</v>
+      </c>
+      <c r="N12" s="3">
+        <v>115000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>117000</v>
+      </c>
+      <c r="P12" s="3">
+        <v>116000</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>113000</v>
+      </c>
+      <c r="R12" s="3">
+        <v>109000</v>
+      </c>
+      <c r="S12" s="3">
+        <v>103000</v>
+      </c>
+      <c r="T12" s="3">
         <v>102000</v>
       </c>
-      <c r="I12" s="3">
-        <v>111000</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="U12" s="3">
+        <v>92000</v>
+      </c>
+      <c r="V12" s="3">
+        <v>197000</v>
+      </c>
+      <c r="W12" s="3">
+        <v>104000</v>
+      </c>
+      <c r="X12" s="3">
+        <v>102000</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>101000</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>99000</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>102000</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>104000</v>
+      </c>
+      <c r="AC12" s="3">
         <v>97000</v>
       </c>
-      <c r="K12" s="3">
-        <v>119000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>116000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>115000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>117000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>116000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>113000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>109000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>103000</v>
-      </c>
-      <c r="S12" s="3">
-        <v>102000</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="AD12" s="3">
         <v>92000</v>
       </c>
-      <c r="U12" s="3">
-        <v>197000</v>
-      </c>
-      <c r="V12" s="3">
-        <v>104000</v>
-      </c>
-      <c r="W12" s="3">
-        <v>102000</v>
-      </c>
-      <c r="X12" s="3">
-        <v>101000</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>99000</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>102000</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>104000</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>97000</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>92000</v>
-      </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>93000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>89000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>87000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>84000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>79000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1332,31 +1348,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>67000</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
+        <v>54000</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
-        <v>3000</v>
-      </c>
       <c r="G14" s="3">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H14" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>295000</v>
+      </c>
+      <c r="J14" s="3">
         <v>9000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1382,20 +1401,20 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>3000</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>3000</v>
       </c>
       <c r="U14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4000</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
@@ -1406,17 +1425,17 @@
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-15000</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1433,31 +1452,34 @@
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1534,8 +1556,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1568,210 +1593,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1245000</v>
+        <v>1293000</v>
       </c>
       <c r="E17" s="3">
-        <v>1210000</v>
+        <v>1184000</v>
       </c>
       <c r="F17" s="3">
-        <v>1274000</v>
+        <v>1200000</v>
       </c>
       <c r="G17" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1326000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1378000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1247000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1298000</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="R17" s="3">
         <v>1237000</v>
       </c>
-      <c r="H17" s="3">
-        <v>1539000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1334000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1330000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1378000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1307000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1247000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1298000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1265000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1250000</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1237000</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1220000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1184000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1031000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1136000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1142000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1117000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1049000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1022000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1034000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1035000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>982000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>996000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>972000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>956000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>913000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>901000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>861000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>928000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>333000</v>
+        <v>408000</v>
       </c>
       <c r="E18" s="3">
-        <v>363000</v>
+        <v>394000</v>
       </c>
       <c r="F18" s="3">
-        <v>384000</v>
+        <v>373000</v>
       </c>
       <c r="G18" s="3">
-        <v>451000</v>
+        <v>399000</v>
       </c>
       <c r="H18" s="3">
-        <v>133000</v>
+        <v>453000</v>
       </c>
       <c r="I18" s="3">
-        <v>383000</v>
+        <v>432000</v>
       </c>
       <c r="J18" s="3">
+        <v>391000</v>
+      </c>
+      <c r="K18" s="3">
         <v>426000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>471000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>411000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>360000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>376000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>395000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>336000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>288000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>328000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>299000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>230000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>102000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>215000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>250000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>225000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>216000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>250000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>259000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>221000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>210000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>239000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>233000</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>201000</v>
       </c>
       <c r="AG18" s="3">
         <v>201000</v>
       </c>
       <c r="AH18" s="3">
+        <v>201000</v>
+      </c>
+      <c r="AI18" s="3">
         <v>206000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1807,242 +1839,249 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>32000</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
-        <v>31000</v>
+        <v>-6000</v>
       </c>
       <c r="F20" s="3">
-        <v>41000</v>
+        <v>-3000</v>
       </c>
       <c r="G20" s="3">
-        <v>-9000</v>
+        <v>-14000</v>
       </c>
       <c r="H20" s="3">
-        <v>23000</v>
+        <v>-41000</v>
       </c>
       <c r="I20" s="3">
-        <v>18000</v>
+        <v>-6000</v>
       </c>
       <c r="J20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="K20" s="3">
         <v>9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-36000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>74000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>3000</v>
       </c>
       <c r="S20" s="3">
         <v>3000</v>
       </c>
       <c r="T20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="U20" s="3">
         <v>8000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>39000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>24000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>15000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>19000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>16000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>39000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>36000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>14000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>13000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>11000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>10000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>428000</v>
+        <v>478000</v>
       </c>
       <c r="E21" s="3">
-        <v>457000</v>
+        <v>463000</v>
       </c>
       <c r="F21" s="3">
-        <v>487000</v>
+        <v>439000</v>
       </c>
       <c r="G21" s="3">
-        <v>504000</v>
+        <v>475000</v>
       </c>
       <c r="H21" s="3">
-        <v>227000</v>
+        <v>556000</v>
       </c>
       <c r="I21" s="3">
-        <v>472000</v>
+        <v>509000</v>
       </c>
       <c r="J21" s="3">
+        <v>469000</v>
+      </c>
+      <c r="K21" s="3">
         <v>502000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>551000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>496000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>436000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>422000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>553000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>432000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>370000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>407000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>378000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>315000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>217000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>318000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>328000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>295000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>288000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>320000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>318000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>313000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>296000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>304000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>298000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>263000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>265000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>268000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>226000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E22" s="3">
         <v>22000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>22000</v>
       </c>
       <c r="G22" s="3">
         <v>22000</v>
       </c>
       <c r="H22" s="3">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="I22" s="3">
         <v>24000</v>
       </c>
       <c r="J22" s="3">
+        <v>24000</v>
+      </c>
+      <c r="K22" s="3">
         <v>25000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>21000</v>
       </c>
       <c r="N22" s="3">
         <v>21000</v>
@@ -2054,10 +2093,10 @@
         <v>21000</v>
       </c>
       <c r="Q22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="R22" s="3">
         <v>20000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>19000</v>
       </c>
       <c r="S22" s="3">
         <v>19000</v>
@@ -2066,22 +2105,22 @@
         <v>19000</v>
       </c>
       <c r="U22" s="3">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="V22" s="3">
         <v>20000</v>
       </c>
       <c r="W22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="X22" s="3">
         <v>21000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>18000</v>
       </c>
       <c r="AA22" s="3">
         <v>18000</v>
@@ -2090,230 +2129,239 @@
         <v>18000</v>
       </c>
       <c r="AC22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>20000</v>
       </c>
       <c r="AE22" s="3">
         <v>20000</v>
       </c>
       <c r="AF22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>20000</v>
       </c>
       <c r="AH22" s="3">
         <v>20000</v>
       </c>
       <c r="AI22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>401000</v>
+      </c>
+      <c r="E23" s="3">
         <v>343000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>374000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>403000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>420000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>132000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>377000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>410000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>455000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>397000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>333000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>319000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>448000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>327000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>273000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>312000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>283000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>219000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>121000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>219000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>231000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>222000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>218000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>248000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>244000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>242000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>227000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>233000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>226000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>193000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>191000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>193000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E24" s="3">
         <v>61000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>66000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>55000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-55000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>75000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>58000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>87000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>68000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>59000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>36000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>57000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>24000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>61000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>20000</v>
       </c>
       <c r="U24" s="3">
         <v>20000</v>
       </c>
       <c r="V24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="W24" s="3">
         <v>22000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>37000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>31000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>36000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-256000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>30000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>22000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>20000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>49000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>27000</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>25000</v>
       </c>
       <c r="AI24" s="3">
         <v>25000</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>25000</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2413,210 +2461,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E26" s="3">
         <v>282000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>308000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>348000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>475000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>111000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>302000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>352000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>368000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>329000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>274000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>283000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>442000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>264000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>216000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>288000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>222000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>199000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>101000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>197000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>194000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>191000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>182000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>504000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>214000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>236000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>205000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>213000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>177000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>175000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>164000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>168000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E27" s="3">
         <v>282000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>308000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>348000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>475000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>111000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>302000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>352000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>368000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>329000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>274000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>283000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>442000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>264000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>216000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>288000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>222000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>199000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>101000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>197000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>194000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>191000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>182000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>504000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>214000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>236000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>205000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>213000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>177000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>175000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>164000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>168000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2716,8 +2773,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2772,8 +2832,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>10</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>10</v>
@@ -2790,23 +2850,23 @@
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-19000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-533000</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>10</v>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>10</v>
@@ -2814,11 +2874,14 @@
       <c r="AH29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2918,8 +2981,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3019,210 +3085,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-32000</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-31000</v>
+        <v>6000</v>
       </c>
       <c r="F32" s="3">
-        <v>-41000</v>
+        <v>3000</v>
       </c>
       <c r="G32" s="3">
-        <v>9000</v>
+        <v>14000</v>
       </c>
       <c r="H32" s="3">
-        <v>-23000</v>
+        <v>41000</v>
       </c>
       <c r="I32" s="3">
-        <v>-18000</v>
+        <v>6000</v>
       </c>
       <c r="J32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>36000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-74000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-3000</v>
       </c>
       <c r="S32" s="3">
         <v>-3000</v>
       </c>
       <c r="T32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U32" s="3">
         <v>-8000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-39000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-24000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E33" s="3">
         <v>282000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>308000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>348000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>475000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>111000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>302000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>352000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>368000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>329000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>274000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>283000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>442000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>264000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>216000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>288000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>222000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>199000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>101000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>197000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>194000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>191000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>182000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>504000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>195000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>236000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>205000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-320000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>177000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>175000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>164000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>168000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3322,215 +3397,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E35" s="3">
         <v>282000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>308000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>348000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>475000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>111000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>302000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>352000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>368000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>329000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>274000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>283000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>442000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>264000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>216000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>288000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>222000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>199000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>101000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>197000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>194000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>191000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>182000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>504000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>195000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>236000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>205000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-320000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>177000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>175000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>164000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>168000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3566,8 +3650,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3603,109 +3688,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1329000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1779000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1671000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1748000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1590000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1329000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1175000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1250000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1053000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1071000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1186000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1113000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1484000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1428000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1380000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1329000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1441000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1358000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1324000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1226000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1382000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1765000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2155000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2057000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2247000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2131000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3011000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2887000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2678000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2389000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3734,19 +3823,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>6000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>21000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>91000</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>10</v>
@@ -3760,8 +3849,8 @@
       <c r="T42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3805,715 +3894,739 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1227000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1249000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1295000</v>
       </c>
-      <c r="G43" s="3">
-        <v>1291000</v>
-      </c>
       <c r="H43" s="3">
+        <v>1391000</v>
+      </c>
+      <c r="I43" s="3">
         <v>1339000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1401000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1459000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1405000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1345000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1237000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1205000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1172000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1122000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1075000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1087000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1038000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>930000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>886000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>966000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>930000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>856000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>819000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>833000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>776000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>733000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>754000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>751000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>724000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>678000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>677000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>653000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>972000</v>
+      </c>
+      <c r="E44" s="3">
         <v>978000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1000000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1033000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1031000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1072000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1103000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1111000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1038000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1010000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>937000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>879000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>830000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>818000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>791000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>755000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>720000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>746000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>750000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>706000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>679000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>660000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>657000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>653000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>638000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>623000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>594000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>608000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>575000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>566000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>548000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>551000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>533000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E45" s="3">
         <v>272000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>283000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>262000</v>
       </c>
-      <c r="G45" s="3">
-        <v>274000</v>
-      </c>
       <c r="H45" s="3">
+        <v>174000</v>
+      </c>
+      <c r="I45" s="3">
         <v>290000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>270000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>258000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>282000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>258000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>262000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>232000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>222000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>264000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>268000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>312000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>216000</v>
-      </c>
-      <c r="T45" s="3">
-        <v>211000</v>
       </c>
       <c r="U45" s="3">
         <v>211000</v>
       </c>
       <c r="V45" s="3">
+        <v>211000</v>
+      </c>
+      <c r="W45" s="3">
         <v>204000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>198000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>176000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>181000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>169000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>187000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>180000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>166000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>151000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>192000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>189000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>186000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>190000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>182000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3959000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4256000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4203000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4338000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4186000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4030000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3949000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4078000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3778000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3690000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3643000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3474000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3799000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3632000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3514000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3483000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3415000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3245000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3171000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3102000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3189000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3457000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3812000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3712000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3848000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3667000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4525000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4397000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4169000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3996000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3800000</v>
-      </c>
-      <c r="AH46" s="3">
-        <v>3635000</v>
       </c>
       <c r="AI46" s="3">
         <v>3635000</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>3635000</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E47" s="3">
         <v>186000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>177000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>170000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>164000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>190000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>186000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>188000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>195000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>194000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>190000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>191000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>185000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>204000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>188000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>165000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>158000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>148000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>141000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>118000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>102000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>99000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>96000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>77000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>68000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>70000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>139000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>140000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>138000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>137000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>134000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>133000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1778000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1624000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1533000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1469000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1424000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1377000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1338000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1147000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1250000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1212000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1172000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1144000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1123000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1087000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1070000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1039000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1020000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1029000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1024000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1035000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>850000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>839000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>827000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>829000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>822000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>801000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>798000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>792000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>757000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>716000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>675000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>653000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5024000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4357000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4380000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4410000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4435000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4486000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4778000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4793000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4773000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4797000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4854000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4893000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4956000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5008000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5059000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4405000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4433000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4482000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4503000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4648000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4700000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3618000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3650000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3699000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3464000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3448000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2932000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2968000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2987000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2933000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4613,8 +4726,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4714,109 +4830,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>910000</v>
+      </c>
+      <c r="E52" s="3">
         <v>573000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>563000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>561000</v>
       </c>
-      <c r="G52" s="3">
-        <v>554000</v>
-      </c>
       <c r="H52" s="3">
+        <v>270000</v>
+      </c>
+      <c r="I52" s="3">
         <v>592000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>541000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>713000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>536000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>591000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>596000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>625000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>642000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>560000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>567000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>582000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>601000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>642000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>616000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>598000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>611000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>612000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>637000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>635000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>339000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>363000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>390000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>395000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>394000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>425000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>466000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>477000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4916,109 +5038,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11846000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10996000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10856000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10948000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10763000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10675000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10792000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10919000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10532000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10484000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10455000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10327000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10705000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10491000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10398000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9674000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9627000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9546000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9455000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9501000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9452000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8625000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9022000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8952000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8541000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8349000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8784000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8698000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8426000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8261000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8016000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7872000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7794000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5054,8 +5182,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5091,614 +5220,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E57" s="3">
         <v>497000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>461000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>488000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>418000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>452000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>479000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>540000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>580000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>558000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>503000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>475000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>446000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>416000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>423000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>398000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>354000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>311000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>333000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>329000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>354000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>316000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>314000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>315000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>340000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>273000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>271000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>292000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>305000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>289000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>265000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>268000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E58" s="3">
         <v>795000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>420000</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>46000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>55000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>238000</v>
+      </c>
+      <c r="L58" s="3">
+        <v>36000</v>
+      </c>
+      <c r="M58" s="3">
+        <v>180000</v>
+      </c>
+      <c r="N58" s="3">
+        <v>175000</v>
+      </c>
+      <c r="O58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>55000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>238000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>36000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>180000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>175000</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>130000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>205000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>314000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>75000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>40000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>675000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>616000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>504000</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>315000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>345000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>210000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>280000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>241000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>190000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1097000</v>
+        <v>544000</v>
       </c>
       <c r="E59" s="3">
-        <v>1077000</v>
+        <v>605000</v>
       </c>
       <c r="F59" s="3">
-        <v>1129000</v>
+        <v>575000</v>
       </c>
       <c r="G59" s="3">
-        <v>1185000</v>
+        <v>544000</v>
       </c>
       <c r="H59" s="3">
-        <v>1253000</v>
+        <v>610000</v>
       </c>
       <c r="I59" s="3">
-        <v>1187000</v>
+        <v>552000</v>
       </c>
       <c r="J59" s="3">
+        <v>565000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1158000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1245000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1164000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1135000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1109000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1262000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1178000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1130000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>975000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1038000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>963000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>912000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>888000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1110000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>802000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>804000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>780000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>831000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>741000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>779000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>724000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>748000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>672000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>681000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>631000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>688000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1895000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2389000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1958000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1617000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1603000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1760000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1666000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1936000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1861000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1902000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1813000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1584000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1708000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1724000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1758000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1687000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1467000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1314000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1945000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1892000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2080000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1622000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1118000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1095000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1171000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1014000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1361000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1263000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1241000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1187000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1089000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2137000</v>
+        <v>3345000</v>
       </c>
       <c r="E61" s="3">
-        <v>2136000</v>
+        <v>2321000</v>
       </c>
       <c r="F61" s="3">
-        <v>2555000</v>
+        <v>2306000</v>
       </c>
       <c r="G61" s="3">
-        <v>2735000</v>
+        <v>2719000</v>
       </c>
       <c r="H61" s="3">
-        <v>2734000</v>
+        <v>2853000</v>
       </c>
       <c r="I61" s="3">
-        <v>2733000</v>
+        <v>2912000</v>
       </c>
       <c r="J61" s="3">
-        <v>2733000</v>
+        <v>2891000</v>
       </c>
       <c r="K61" s="3">
         <v>2733000</v>
       </c>
       <c r="L61" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="M61" s="3">
         <v>2732000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2730000</v>
       </c>
       <c r="N61" s="3">
         <v>2730000</v>
       </c>
       <c r="O61" s="3">
+        <v>2730000</v>
+      </c>
+      <c r="P61" s="3">
         <v>2729000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2728000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2727000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2185000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2284000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2283000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1788000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1787000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1791000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1294000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>1798000</v>
       </c>
       <c r="Z61" s="3">
         <v>1798000</v>
       </c>
       <c r="AA61" s="3">
-        <v>1799000</v>
+        <v>1798000</v>
       </c>
       <c r="AB61" s="3">
         <v>1799000</v>
       </c>
       <c r="AC61" s="3">
-        <v>1800000</v>
+        <v>1799000</v>
       </c>
       <c r="AD61" s="3">
         <v>1800000</v>
       </c>
       <c r="AE61" s="3">
-        <v>1801000</v>
+        <v>1800000</v>
       </c>
       <c r="AF61" s="3">
         <v>1801000</v>
       </c>
       <c r="AG61" s="3">
-        <v>1802000</v>
+        <v>1801000</v>
       </c>
       <c r="AH61" s="3">
         <v>1802000</v>
       </c>
       <c r="AI61" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>567000</v>
+        <v>578000</v>
       </c>
       <c r="E62" s="3">
-        <v>548000</v>
+        <v>165000</v>
       </c>
       <c r="F62" s="3">
-        <v>588000</v>
+        <v>158000</v>
       </c>
       <c r="G62" s="3">
-        <v>580000</v>
+        <v>200000</v>
       </c>
       <c r="H62" s="3">
-        <v>623000</v>
+        <v>210000</v>
       </c>
       <c r="I62" s="3">
-        <v>612000</v>
+        <v>243000</v>
       </c>
       <c r="J62" s="3">
+        <v>250000</v>
+      </c>
+      <c r="K62" s="3">
         <v>641000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>633000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>759000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>790000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>859000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>879000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1093000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1103000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>998000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1003000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>968000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>954000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>974000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>833000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>962000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>981000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1023000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1000000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>968000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1011000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>527000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>608000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>652000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>681000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5798,8 +5946,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5899,8 +6050,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6000,109 +6154,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5948000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5093000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4642000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4760000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4918000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5117000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5011000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5310000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5227000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5393000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5333000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5173000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5316000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5545000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5588000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4870000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4754000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4565000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4687000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4653000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4704000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3878000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3897000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3916000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3974000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3785000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4171000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4176000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3595000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3653000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3644000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3575000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3551000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6138,8 +6298,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6239,8 +6400,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6340,8 +6504,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6441,8 +6608,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6542,109 +6712,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E72" s="3">
         <v>773000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1090000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1061000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>782000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>444000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>700000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>541000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>324000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>139000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>160000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>159000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>348000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>90000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>81000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>130000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>73000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-18000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-122000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>178000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>90000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-336000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-416000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-412000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-529000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-126000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-393000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6089000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6744,8 +6920,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6845,8 +7024,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6946,109 +7128,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5898000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5903000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6214000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6188000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5845000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5558000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5781000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5609000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5305000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5091000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5122000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5154000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5389000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4946000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4810000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4804000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4873000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4981000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4768000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4848000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4748000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4747000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5125000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5036000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4567000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4564000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4613000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4522000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4831000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4608000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4372000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4297000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4243000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7148,215 +7336,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E81" s="3">
         <v>282000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>308000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>348000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>475000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>111000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>302000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>352000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>368000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>329000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>274000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>283000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>442000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>264000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>216000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>288000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>222000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>199000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>101000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>197000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>194000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>191000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>182000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>504000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>195000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>236000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>205000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-320000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>177000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>175000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>164000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>168000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7392,109 +7589,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>63000</v>
+        <v>35000</v>
       </c>
       <c r="E83" s="3">
-        <v>63000</v>
+        <v>32000</v>
       </c>
       <c r="F83" s="3">
-        <v>62000</v>
+        <v>33000</v>
       </c>
       <c r="G83" s="3">
-        <v>62000</v>
+        <v>31000</v>
       </c>
       <c r="H83" s="3">
-        <v>71000</v>
+        <v>31000</v>
       </c>
       <c r="I83" s="3">
-        <v>71000</v>
+        <v>32000</v>
       </c>
       <c r="J83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K83" s="3">
         <v>67000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>73000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>82000</v>
       </c>
       <c r="N83" s="3">
         <v>82000</v>
       </c>
       <c r="O83" s="3">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="P83" s="3">
         <v>84000</v>
       </c>
       <c r="Q83" s="3">
+        <v>84000</v>
+      </c>
+      <c r="R83" s="3">
         <v>77000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>76000</v>
       </c>
       <c r="S83" s="3">
         <v>76000</v>
       </c>
       <c r="T83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="U83" s="3">
         <v>77000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>76000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>79000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>76000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>55000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>53000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>54000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>56000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>53000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>50000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>51000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>52000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>51000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>54000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>55000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7594,8 +7795,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7695,8 +7899,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7796,8 +8003,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7897,8 +8107,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7998,109 +8211,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>481000</v>
+      </c>
+      <c r="E89" s="3">
         <v>452000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>333000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>485000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>516000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>562000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>398000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>296000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>448000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>326000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>283000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>255000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>441000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>334000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>472000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>238000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>377000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>290000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>313000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-59000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>314000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>242000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>252000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>213000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>372000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>197000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>303000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>215000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>288000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>228000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>257000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>116000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8136,109 +8355,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-92000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-103000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-90000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-84000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-81000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-57000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-76000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-70000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-82000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-64000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-75000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-62000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-41000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-33000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-34000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-30000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-39000</v>
       </c>
       <c r="Z91" s="3">
         <v>-39000</v>
       </c>
       <c r="AA91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-58000</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-43000</v>
       </c>
       <c r="AG91" s="3">
         <v>-43000</v>
       </c>
       <c r="AH91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8338,8 +8561,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8439,109 +8665,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-954000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-109000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-95000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-89000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-77000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-104000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-110000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-73000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-76000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-79000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-59000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-61000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-587000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-42000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-32000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-53000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-51000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-290000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-473000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-78000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8577,46 +8809,47 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-68000</v>
+        <v>68000</v>
       </c>
       <c r="E96" s="3">
-        <v>-69000</v>
+        <v>68000</v>
       </c>
       <c r="F96" s="3">
-        <v>-69000</v>
+        <v>69000</v>
       </c>
       <c r="G96" s="3">
-        <v>-66000</v>
+        <v>69000</v>
       </c>
       <c r="H96" s="3">
-        <v>-66000</v>
+        <v>66000</v>
       </c>
       <c r="I96" s="3">
-        <v>-66000</v>
+        <v>66000</v>
       </c>
       <c r="J96" s="3">
+        <v>66000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-67000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-62000</v>
       </c>
       <c r="L96" s="3">
         <v>-62000</v>
       </c>
       <c r="M96" s="3">
-        <v>-63000</v>
+        <v>-62000</v>
       </c>
       <c r="N96" s="3">
         <v>-63000</v>
       </c>
       <c r="O96" s="3">
-        <v>-59000</v>
+        <v>-63000</v>
       </c>
       <c r="P96" s="3">
         <v>-59000</v>
@@ -8628,34 +8861,34 @@
         <v>-59000</v>
       </c>
       <c r="S96" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-55000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-56000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-55000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-56000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-51000</v>
       </c>
       <c r="X96" s="3">
         <v>-51000</v>
       </c>
       <c r="Y96" s="3">
-        <v>-52000</v>
+        <v>-51000</v>
       </c>
       <c r="Z96" s="3">
         <v>-52000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-48000</v>
       </c>
       <c r="AC96" s="3">
         <v>-48000</v>
@@ -8664,22 +8897,25 @@
         <v>-48000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8779,8 +9015,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8880,8 +9119,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8981,307 +9223,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-246000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-291000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-240000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-201000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-322000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-390000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-341000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-362000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-123000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-546000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-324000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>166000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-316000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-269000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-231000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-156000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-61000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>497000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-582000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-92000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-122000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-131000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-589000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>37000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>29000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-56000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2000</v>
+        <v>-14000</v>
       </c>
       <c r="E101" s="3">
-        <v>-9000</v>
+        <v>3000</v>
       </c>
       <c r="F101" s="3">
-        <v>7000</v>
+        <v>-6000</v>
       </c>
       <c r="G101" s="3">
+        <v>22000</v>
+      </c>
+      <c r="H101" s="3">
         <v>-14000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>3000</v>
       </c>
       <c r="I101" s="3">
         <v>-6000</v>
       </c>
       <c r="J101" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K101" s="3">
         <v>22000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-12000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-3000</v>
       </c>
       <c r="P101" s="3">
         <v>-3000</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>9000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-1000</v>
       </c>
       <c r="W101" s="3">
         <v>-1000</v>
       </c>
       <c r="X101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>9000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-15000</v>
       </c>
       <c r="AC101" s="3">
         <v>-15000</v>
       </c>
       <c r="AD101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AE101" s="3">
         <v>24000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>18000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-450000</v>
+      </c>
+      <c r="E102" s="3">
         <v>108000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-76000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>157000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>261000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>154000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>197000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-115000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>72000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-374000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>55000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>48000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>51000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-111000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>83000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>35000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>97000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-156000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-383000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-390000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>97000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-190000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>116000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-880000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>124000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>209000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>115000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>174000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>148000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>90000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>A</t>
   </si>
@@ -656,457 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1701000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1578000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1573000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1658000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1688000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1672000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1717000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1756000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1849000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1718000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1607000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1674000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1660000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1586000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1525000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1548000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1483000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1261000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1238000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1357000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1367000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1274000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1238000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1284000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1294000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1203000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1206000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1211000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1189000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1114000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1102000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1111000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>782000</v>
+      </c>
+      <c r="E9" s="3">
         <v>785000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>723000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>717000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>750000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>773000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1014000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>793000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>788000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>837000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>779000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>746000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>764000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>760000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>734000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>708000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>710000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>695000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>592000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>583000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>634000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>628000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>581000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>569000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>572000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>576000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>545000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>558000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>538000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>540000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>519000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>511000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>494000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>899000</v>
+      </c>
+      <c r="E10" s="3">
         <v>916000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>855000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>856000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>908000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>915000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>658000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>924000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>968000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1012000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>939000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>861000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>910000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>900000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>852000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>817000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>838000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>788000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>669000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>655000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>723000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>739000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>693000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>669000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>712000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>718000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>658000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>648000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>673000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>649000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>595000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>591000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>573000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1143,112 +1155,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>111000</v>
+        <v>113000</v>
       </c>
       <c r="E12" s="3">
+        <v>131000</v>
+      </c>
+      <c r="F12" s="3">
         <v>109000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>113000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>120000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>114000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>118000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>126000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>97000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>119000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>116000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>115000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>117000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>116000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>113000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>109000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>103000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>102000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>92000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>197000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>104000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>102000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>101000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>99000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>102000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>104000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>97000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>92000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>93000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>89000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>87000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>84000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>79000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1351,34 +1367,37 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="F14" s="3">
         <v>54000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6000</v>
       </c>
-      <c r="H14" s="3">
-        <v>69000</v>
-      </c>
       <c r="I14" s="3">
+        <v>-273000</v>
+      </c>
+      <c r="J14" s="3">
         <v>295000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -1404,20 +1423,20 @@
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>3000</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>3000</v>
       </c>
       <c r="V14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4000</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
@@ -1428,17 +1447,17 @@
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-15000</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
@@ -1455,34 +1474,37 @@
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E15" s="3">
         <v>69000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>63000</v>
       </c>
       <c r="F15" s="3">
         <v>63000</v>
       </c>
       <c r="G15" s="3">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="H15" s="3">
         <v>62000</v>
       </c>
       <c r="I15" s="3">
-        <v>71000</v>
+        <v>62000</v>
       </c>
       <c r="J15" s="3">
         <v>71000</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1559,8 +1581,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1594,216 +1619,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1293000</v>
+        <v>1291000</v>
       </c>
       <c r="E17" s="3">
+        <v>1326000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1184000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1200000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1259000</v>
       </c>
-      <c r="H17" s="3">
-        <v>1235000</v>
-      </c>
       <c r="I17" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="J17" s="3">
         <v>1240000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1326000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1330000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1378000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1307000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1247000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1298000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1265000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1250000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1237000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1220000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1184000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1031000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1136000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1142000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1117000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1049000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1022000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1034000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1035000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>982000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>996000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>972000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>956000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>913000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>901000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>861000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>928000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>408000</v>
+        <v>390000</v>
       </c>
       <c r="E18" s="3">
+        <v>375000</v>
+      </c>
+      <c r="F18" s="3">
         <v>394000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>373000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>399000</v>
       </c>
-      <c r="H18" s="3">
-        <v>453000</v>
-      </c>
       <c r="I18" s="3">
+        <v>154000</v>
+      </c>
+      <c r="J18" s="3">
         <v>432000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>391000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>426000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>471000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>411000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>360000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>376000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>395000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>336000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>288000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>328000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>299000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>230000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>102000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>215000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>250000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>225000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>216000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>250000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>259000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>221000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>210000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>239000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>233000</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>201000</v>
       </c>
       <c r="AH18" s="3">
         <v>201000</v>
       </c>
       <c r="AI18" s="3">
+        <v>201000</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>206000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1840,251 +1872,258 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1000</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-14000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-41000</v>
-      </c>
       <c r="I20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-36000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>74000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>3000</v>
       </c>
       <c r="T20" s="3">
         <v>3000</v>
       </c>
       <c r="U20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V20" s="3">
         <v>8000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>39000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>24000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>15000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>19000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>16000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>39000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>36000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>14000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>13000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>11000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>478000</v>
+        <v>452000</v>
       </c>
       <c r="E21" s="3">
+        <v>437000</v>
+      </c>
+      <c r="F21" s="3">
         <v>463000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>439000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>475000</v>
       </c>
-      <c r="H21" s="3">
-        <v>556000</v>
-      </c>
       <c r="I21" s="3">
+        <v>214000</v>
+      </c>
+      <c r="J21" s="3">
         <v>509000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>469000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>502000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>551000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>496000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>436000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>422000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>553000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>432000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>370000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>407000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>378000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>315000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>217000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>318000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>328000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>295000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>288000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>320000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>318000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>313000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>296000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>304000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>298000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>263000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>265000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>268000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>226000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E22" s="3">
         <v>32000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>22000</v>
       </c>
       <c r="H22" s="3">
         <v>22000</v>
       </c>
       <c r="I22" s="3">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="J22" s="3">
         <v>24000</v>
       </c>
       <c r="K22" s="3">
+        <v>24000</v>
+      </c>
+      <c r="L22" s="3">
         <v>25000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>21000</v>
       </c>
       <c r="O22" s="3">
         <v>21000</v>
@@ -2096,10 +2135,10 @@
         <v>21000</v>
       </c>
       <c r="R22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="S22" s="3">
         <v>20000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>19000</v>
       </c>
       <c r="T22" s="3">
         <v>19000</v>
@@ -2108,22 +2147,22 @@
         <v>19000</v>
       </c>
       <c r="V22" s="3">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="W22" s="3">
         <v>20000</v>
       </c>
       <c r="X22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>21000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>18000</v>
       </c>
       <c r="AB22" s="3">
         <v>18000</v>
@@ -2132,236 +2171,245 @@
         <v>18000</v>
       </c>
       <c r="AD22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>20000</v>
       </c>
       <c r="AF22" s="3">
         <v>20000</v>
       </c>
       <c r="AG22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>20000</v>
       </c>
       <c r="AI22" s="3">
         <v>20000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E23" s="3">
         <v>401000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>343000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>374000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>403000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>420000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>132000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>377000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>410000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>455000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>397000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>333000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>319000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>448000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>327000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>273000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>312000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>283000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>219000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>121000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>219000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>231000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>222000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>218000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>248000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>244000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>242000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>227000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>233000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>226000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>193000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>191000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>193000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E24" s="3">
         <v>50000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>61000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>66000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>55000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-55000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>75000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>58000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>87000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>68000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>59000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>36000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>63000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>57000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>61000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>20000</v>
       </c>
       <c r="V24" s="3">
         <v>20000</v>
       </c>
       <c r="W24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="X24" s="3">
         <v>22000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>37000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>36000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-256000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>30000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>22000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>20000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>49000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>27000</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>25000</v>
       </c>
       <c r="AJ24" s="3">
         <v>25000</v>
       </c>
+      <c r="AK24" s="3">
+        <v>25000</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2464,216 +2512,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E26" s="3">
         <v>351000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>282000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>308000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>348000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>475000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>111000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>302000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>352000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>368000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>329000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>274000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>283000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>442000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>264000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>216000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>288000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>222000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>199000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>101000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>197000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>194000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>191000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>182000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>504000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>214000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>236000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>205000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>213000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>177000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>175000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>164000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E27" s="3">
         <v>351000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>282000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>308000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>348000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>475000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>111000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>302000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>352000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>368000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>329000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>274000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>283000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>442000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>264000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>216000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>288000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>222000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>199000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>101000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>197000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>194000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>191000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>182000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>504000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>214000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>236000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>205000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>213000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>177000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>175000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>164000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2776,8 +2833,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2835,8 +2895,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>10</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
@@ -2853,23 +2913,23 @@
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-19000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-533000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>10</v>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>10</v>
@@ -2877,11 +2937,14 @@
       <c r="AI29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2984,8 +3047,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3088,216 +3154,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1000</v>
+        <v>-10000</v>
       </c>
       <c r="E32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F32" s="3">
         <v>6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>14000</v>
       </c>
-      <c r="H32" s="3">
-        <v>41000</v>
-      </c>
       <c r="I32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>36000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-3000</v>
       </c>
       <c r="T32" s="3">
         <v>-3000</v>
       </c>
       <c r="U32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V32" s="3">
         <v>-8000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-39000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-24000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E33" s="3">
         <v>351000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>282000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>308000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>348000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>475000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>111000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>302000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>352000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>368000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>329000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>274000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>283000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>442000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>264000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>216000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>288000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>222000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>199000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>101000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>197000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>194000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>191000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>182000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>504000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>195000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>236000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>205000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-320000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>177000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>175000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>164000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3400,221 +3475,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E35" s="3">
         <v>351000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>282000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>308000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>348000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>475000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>111000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>302000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>352000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>368000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>329000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>274000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>283000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>442000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>264000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>216000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>288000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>222000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>199000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>101000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>197000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>194000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>191000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>182000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>504000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>195000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>236000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>205000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-320000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>177000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>175000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>164000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3651,8 +3735,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3689,112 +3774,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1467000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1329000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1779000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1671000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1748000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1590000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1329000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1175000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1250000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1053000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1071000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1186000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1113000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1484000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1428000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1380000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1329000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1441000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1358000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1324000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1226000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1382000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1765000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2155000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2057000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2247000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2131000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3011000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2887000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2678000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2389000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3826,19 +3915,19 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>6000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>91000</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>10</v>
@@ -3852,8 +3941,8 @@
       <c r="U42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3897,736 +3986,760 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1324000</v>
+        <v>1328000</v>
       </c>
       <c r="E43" s="3">
+        <v>1471000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1227000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1249000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1295000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1391000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1339000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1401000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1459000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1405000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1345000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1237000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1205000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1172000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1122000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1075000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1087000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1038000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>930000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>886000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>966000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>930000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>856000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>819000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>833000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>776000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>733000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>754000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>751000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>724000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>678000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>677000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>653000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>997000</v>
+      </c>
+      <c r="E44" s="3">
         <v>972000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>978000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1000000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1033000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1031000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1072000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1103000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1111000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1038000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1010000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>937000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>879000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>830000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>818000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>791000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>755000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>720000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>746000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>750000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>706000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>679000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>660000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>657000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>653000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>638000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>623000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>594000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>608000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>575000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>566000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>548000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>551000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>533000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>334000</v>
+        <v>315000</v>
       </c>
       <c r="E45" s="3">
+        <v>187000</v>
+      </c>
+      <c r="F45" s="3">
         <v>272000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>283000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>262000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>174000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>290000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>270000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>258000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>282000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>258000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>262000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>232000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>222000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>264000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>268000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>312000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>216000</v>
-      </c>
-      <c r="U45" s="3">
-        <v>211000</v>
       </c>
       <c r="V45" s="3">
         <v>211000</v>
       </c>
       <c r="W45" s="3">
+        <v>211000</v>
+      </c>
+      <c r="X45" s="3">
         <v>204000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>198000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>176000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>181000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>169000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>187000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>180000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>166000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>151000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>192000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>189000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>186000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>190000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>182000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4107000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3959000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4256000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4203000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4338000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4186000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4030000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3949000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4078000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3778000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3690000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3643000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3474000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3799000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3632000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3514000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3483000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3415000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3245000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3171000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3102000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3189000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3457000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3812000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3712000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3848000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3667000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4525000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4397000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4169000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3996000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3800000</v>
-      </c>
-      <c r="AI46" s="3">
-        <v>3635000</v>
       </c>
       <c r="AJ46" s="3">
         <v>3635000</v>
       </c>
+      <c r="AK46" s="3">
+        <v>3635000</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E47" s="3">
         <v>175000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>186000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>177000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>170000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>164000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>190000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>186000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>188000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>195000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>194000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>190000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>191000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>185000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>204000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>188000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>165000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>158000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>148000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>141000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>118000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>102000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>99000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>96000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>77000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>68000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>70000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>139000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>140000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>138000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>137000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>134000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>133000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1778000</v>
+        <v>1988000</v>
       </c>
       <c r="E48" s="3">
+        <v>1955000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1624000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1533000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1469000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1424000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1377000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1338000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1147000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1250000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1212000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1172000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1144000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1087000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1070000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1039000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1020000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1029000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1024000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1035000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>850000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>839000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>827000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>829000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>822000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>801000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>798000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>792000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>757000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>716000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>675000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>653000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4943000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5024000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4357000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4380000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4410000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4435000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4486000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4778000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4793000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4773000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4797000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4854000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4893000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4956000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5008000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5059000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4405000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4433000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4482000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4503000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4648000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4700000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3618000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3650000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3699000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3464000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3448000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2932000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2968000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2987000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2933000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4729,8 +4842,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4833,112 +4949,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>910000</v>
+        <v>703000</v>
       </c>
       <c r="E52" s="3">
+        <v>382000</v>
+      </c>
+      <c r="F52" s="3">
         <v>573000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>563000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>561000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>270000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>592000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>541000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>713000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>536000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>591000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>596000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>625000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>642000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>560000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>567000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>582000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>601000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>642000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>616000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>598000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>611000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>612000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>637000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>635000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>339000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>363000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>390000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>395000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>394000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>425000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>466000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>477000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5041,112 +5163,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11914000</v>
+      </c>
+      <c r="E54" s="3">
         <v>11846000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10996000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10856000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10948000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10763000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10675000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10792000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10919000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10532000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10484000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10455000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10327000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10705000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10491000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10398000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9674000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9627000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9546000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9455000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9501000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9452000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8625000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9022000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8952000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8541000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8349000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8784000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8698000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8426000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8261000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8016000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7872000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7794000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5183,8 +5311,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5221,632 +5350,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>547000</v>
+      </c>
+      <c r="E57" s="3">
         <v>540000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>497000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>461000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>488000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>418000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>452000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>479000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>540000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>580000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>558000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>503000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>475000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>446000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>416000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>423000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>398000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>354000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>311000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>333000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>329000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>354000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>316000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>314000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>315000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>340000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>273000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>271000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>292000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>305000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>289000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>265000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>268000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>45000</v>
+        <v>16000</v>
       </c>
       <c r="E58" s="3">
+        <v>87000</v>
+      </c>
+      <c r="F58" s="3">
         <v>795000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>420000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>46000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>55000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>238000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>36000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>180000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>175000</v>
       </c>
-      <c r="O58" s="3" t="s">
+      <c r="P58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>130000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>205000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>314000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>75000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>40000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>700000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>675000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>616000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>504000</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
       </c>
       <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
         <v>315000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>345000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>210000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>280000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>241000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>190000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>645000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>738000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>608000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>575000</v>
+      </c>
+      <c r="H59" s="3">
         <v>544000</v>
       </c>
-      <c r="E59" s="3">
-        <v>605000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>575000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>544000</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>610000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>552000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>565000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1158000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1245000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1164000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1135000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1109000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1262000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1178000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1130000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>975000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1038000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>963000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>912000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>888000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1110000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>802000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>804000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>780000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>831000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>741000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>779000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>724000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>748000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>672000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>681000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>631000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>688000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1869000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1895000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2389000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1958000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1617000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1603000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1760000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1666000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1936000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1861000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1902000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1813000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1584000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1708000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1724000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1758000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1687000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1467000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1314000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1945000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1892000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2080000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1622000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1118000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1095000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1171000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1014000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1361000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1263000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1241000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1187000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1089000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3345000</v>
+        <v>3524000</v>
       </c>
       <c r="E61" s="3">
+        <v>3487000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2321000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2306000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2719000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2853000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2912000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2891000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2733000</v>
       </c>
       <c r="L61" s="3">
         <v>2733000</v>
       </c>
       <c r="M61" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="N61" s="3">
         <v>2732000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2730000</v>
       </c>
       <c r="O61" s="3">
         <v>2730000</v>
       </c>
       <c r="P61" s="3">
+        <v>2730000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2729000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2728000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2727000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2185000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2284000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2283000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1788000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1787000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1791000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1294000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>1798000</v>
       </c>
       <c r="AA61" s="3">
         <v>1798000</v>
       </c>
       <c r="AB61" s="3">
-        <v>1799000</v>
+        <v>1798000</v>
       </c>
       <c r="AC61" s="3">
         <v>1799000</v>
       </c>
       <c r="AD61" s="3">
-        <v>1800000</v>
+        <v>1799000</v>
       </c>
       <c r="AE61" s="3">
         <v>1800000</v>
       </c>
       <c r="AF61" s="3">
-        <v>1801000</v>
+        <v>1800000</v>
       </c>
       <c r="AG61" s="3">
         <v>1801000</v>
       </c>
       <c r="AH61" s="3">
-        <v>1802000</v>
+        <v>1801000</v>
       </c>
       <c r="AI61" s="3">
         <v>1802000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>578000</v>
+        <v>204000</v>
       </c>
       <c r="E62" s="3">
+        <v>194000</v>
+      </c>
+      <c r="F62" s="3">
         <v>165000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>158000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>210000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>243000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>250000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>641000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>633000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>759000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>790000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>859000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>879000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1093000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1103000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>998000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1003000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>968000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>954000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>974000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>833000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>962000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>981000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1023000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1000000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>968000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1002000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1011000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>527000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>608000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>652000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>681000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5949,8 +6097,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6053,8 +6204,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6157,112 +6311,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5887000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5948000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5093000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4642000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4760000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4918000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5117000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5011000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5310000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5227000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5393000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5333000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5173000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5316000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5545000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5588000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4870000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4754000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4565000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4687000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4653000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4704000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3878000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3897000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3916000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3974000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3785000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4171000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4176000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3595000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3653000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3644000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3575000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3551000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6299,8 +6459,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6403,8 +6564,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6507,8 +6671,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6611,8 +6778,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6715,112 +6885,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>916000</v>
+      </c>
+      <c r="E72" s="3">
         <v>750000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>773000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1090000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1061000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>782000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>444000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>700000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>541000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>324000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>139000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>160000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>159000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>348000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>90000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>81000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>130000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>73000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-122000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>178000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>90000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-336000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-416000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-412000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-529000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-126000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-393000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6089000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6923,8 +7099,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7027,8 +7206,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7131,112 +7313,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6027000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5898000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5903000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6214000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6188000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5845000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5558000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5781000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5609000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5305000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5091000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5122000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5154000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5389000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4946000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4810000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4804000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4873000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4981000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4768000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4848000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4748000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4747000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5125000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5036000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4567000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4564000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4613000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4522000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4831000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4608000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4372000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4297000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4243000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7339,221 +7527,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E81" s="3">
         <v>351000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>282000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>308000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>348000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>475000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>111000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>302000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>352000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>368000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>329000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>274000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>283000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>442000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>264000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>216000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>288000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>222000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>199000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>101000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>197000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>194000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>191000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>182000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>504000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>195000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>236000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>205000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-320000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>177000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>175000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>164000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7590,112 +7787,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E83" s="3">
         <v>35000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>31000</v>
       </c>
       <c r="H83" s="3">
         <v>31000</v>
       </c>
       <c r="I83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J83" s="3">
         <v>32000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>31000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>73000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>80000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>82000</v>
       </c>
       <c r="O83" s="3">
         <v>82000</v>
       </c>
       <c r="P83" s="3">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="Q83" s="3">
         <v>84000</v>
       </c>
       <c r="R83" s="3">
+        <v>84000</v>
+      </c>
+      <c r="S83" s="3">
         <v>77000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>76000</v>
       </c>
       <c r="T83" s="3">
         <v>76000</v>
       </c>
       <c r="U83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="V83" s="3">
         <v>77000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>76000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>79000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>76000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>55000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>53000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>54000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>56000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>53000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>51000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>52000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>51000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>54000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7798,8 +7999,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7902,8 +8106,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8006,8 +8213,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8110,8 +8320,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8214,112 +8427,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>431000</v>
+      </c>
+      <c r="E89" s="3">
         <v>481000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>452000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>333000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>485000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>516000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>562000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>398000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>296000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>448000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>326000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>283000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>255000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>441000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>334000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>472000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>238000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>377000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>290000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>313000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-59000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>314000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>242000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>252000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>213000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>372000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>197000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>303000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>215000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>288000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>228000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>257000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>116000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8356,112 +8575,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-93000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-92000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-103000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-90000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-84000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-81000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-57000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-76000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-70000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-82000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-64000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-75000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-55000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-41000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-25000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-33000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-34000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-39000</v>
       </c>
       <c r="AA91" s="3">
         <v>-39000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-58000</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-43000</v>
       </c>
       <c r="AH91" s="3">
         <v>-43000</v>
       </c>
       <c r="AI91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8564,8 +8787,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8668,112 +8894,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-954000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-109000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-95000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-40000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-89000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-77000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-104000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-110000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-73000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-76000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-79000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-61000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-587000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-42000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-53000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-51000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-290000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-473000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-43000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-78000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8810,25 +9042,26 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>68000</v>
+        <v>71000</v>
       </c>
       <c r="E96" s="3">
         <v>68000</v>
       </c>
       <c r="F96" s="3">
-        <v>69000</v>
+        <v>68000</v>
       </c>
       <c r="G96" s="3">
         <v>69000</v>
       </c>
       <c r="H96" s="3">
-        <v>66000</v>
+        <v>69000</v>
       </c>
       <c r="I96" s="3">
         <v>66000</v>
@@ -8837,22 +9070,22 @@
         <v>66000</v>
       </c>
       <c r="K96" s="3">
+        <v>66000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-67000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-62000</v>
       </c>
       <c r="M96" s="3">
         <v>-62000</v>
       </c>
       <c r="N96" s="3">
-        <v>-63000</v>
+        <v>-62000</v>
       </c>
       <c r="O96" s="3">
         <v>-63000</v>
       </c>
       <c r="P96" s="3">
-        <v>-59000</v>
+        <v>-63000</v>
       </c>
       <c r="Q96" s="3">
         <v>-59000</v>
@@ -8864,34 +9097,34 @@
         <v>-59000</v>
       </c>
       <c r="T96" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-55000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-56000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-55000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-56000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-51000</v>
       </c>
       <c r="Y96" s="3">
         <v>-51000</v>
       </c>
       <c r="Z96" s="3">
-        <v>-52000</v>
+        <v>-51000</v>
       </c>
       <c r="AA96" s="3">
         <v>-52000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-48000</v>
       </c>
       <c r="AD96" s="3">
         <v>-48000</v>
@@ -8900,22 +9133,25 @@
         <v>-48000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9018,8 +9254,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9122,8 +9361,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9226,316 +9468,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-180000</v>
+      </c>
+      <c r="E100" s="3">
         <v>25000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-246000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-291000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-240000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-201000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-322000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-390000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-341000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-362000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-123000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-546000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-324000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-222000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>166000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-316000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-269000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-231000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-156000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-61000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>497000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-582000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-122000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-131000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-589000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>37000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>29000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-56000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>22000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>22000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-6000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-3000</v>
       </c>
       <c r="Q101" s="3">
         <v>-3000</v>
       </c>
       <c r="R101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-1000</v>
       </c>
       <c r="X101" s="3">
         <v>-1000</v>
       </c>
       <c r="Y101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>9000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-15000</v>
       </c>
       <c r="AD101" s="3">
         <v>-15000</v>
       </c>
       <c r="AE101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AF101" s="3">
         <v>24000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>18000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-450000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>108000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-76000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>157000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>261000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>154000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-75000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>197000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-115000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>72000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-374000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>55000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>48000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>51000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-111000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>83000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>97000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-156000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-383000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-390000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>97000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-190000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>116000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-880000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>124000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>209000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>115000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>174000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>148000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>90000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
@@ -656,469 +656,481 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1668000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1681000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1701000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1578000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1573000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1658000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1688000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1672000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1717000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1756000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1849000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1718000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1607000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1674000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1660000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1586000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1525000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1548000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1483000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1261000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1238000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1357000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1367000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1274000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1238000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1284000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1294000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1203000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1206000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1211000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1189000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1114000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1102000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1111000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>787000</v>
+      </c>
+      <c r="E9" s="3">
         <v>782000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>785000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>723000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>717000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>750000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>773000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1014000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>793000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>788000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>837000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>779000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>746000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>764000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>760000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>734000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>708000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>710000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>695000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>592000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>583000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>634000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>628000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>581000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>569000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>572000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>576000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>545000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>558000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>538000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>540000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>519000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>511000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>494000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>881000</v>
+      </c>
+      <c r="E10" s="3">
         <v>899000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>916000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>855000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>856000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>908000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>915000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>658000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>924000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>968000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1012000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>939000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>861000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>910000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>900000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>852000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>817000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>838000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>788000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>669000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>655000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>723000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>739000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>693000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>669000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>712000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>718000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>658000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>648000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>673000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>649000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>595000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>591000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>573000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1156,115 +1168,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E12" s="3">
         <v>113000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>131000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>109000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>113000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>120000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>114000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>118000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>126000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>97000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>119000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>116000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>115000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>117000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>116000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>113000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>109000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>103000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>102000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>92000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>197000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>104000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>102000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>101000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>99000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>102000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>104000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>97000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>92000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>93000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>89000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>87000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>84000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>79000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1370,37 +1386,40 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-41000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>54000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-273000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>295000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -1426,20 +1445,20 @@
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>3000</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
         <v>3000</v>
       </c>
       <c r="W14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="X14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4000</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
@@ -1450,17 +1469,17 @@
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-15000</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
@@ -1477,37 +1496,40 @@
       <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E15" s="3">
         <v>72000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>69000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>63000</v>
       </c>
       <c r="G15" s="3">
         <v>63000</v>
       </c>
       <c r="H15" s="3">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="I15" s="3">
         <v>62000</v>
       </c>
       <c r="J15" s="3">
-        <v>71000</v>
+        <v>62000</v>
       </c>
       <c r="K15" s="3">
         <v>71000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1584,8 +1606,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1620,222 +1645,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1275000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1291000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1326000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1184000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1200000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1259000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1534000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1240000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1326000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1330000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1378000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1307000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1247000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1265000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1250000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1237000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1220000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1184000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1031000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1136000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1142000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1117000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1049000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1022000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1034000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1035000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>982000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>996000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>972000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>956000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>913000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>901000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>861000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>928000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E18" s="3">
         <v>390000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>375000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>394000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>373000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>399000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>154000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>432000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>391000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>426000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>471000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>411000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>360000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>376000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>395000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>336000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>288000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>328000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>299000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>230000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>102000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>215000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>250000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>225000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>216000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>250000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>259000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>221000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>210000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>239000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>233000</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>201000</v>
       </c>
       <c r="AI18" s="3">
         <v>201000</v>
       </c>
       <c r="AJ18" s="3">
+        <v>201000</v>
+      </c>
+      <c r="AK18" s="3">
         <v>206000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1873,8 +1905,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1882,251 +1915,257 @@
         <v>10000</v>
       </c>
       <c r="E20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F20" s="3">
         <v>7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>74000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>3000</v>
       </c>
       <c r="U20" s="3">
         <v>3000</v>
       </c>
       <c r="V20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W20" s="3">
         <v>8000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>39000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>24000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>15000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>19000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>16000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>39000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>36000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>14000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>13000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>11000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E21" s="3">
         <v>452000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>437000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>463000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>439000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>475000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>214000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>509000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>469000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>502000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>551000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>496000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>436000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>422000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>553000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>432000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>370000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>407000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>378000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>315000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>217000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>318000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>328000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>295000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>288000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>320000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>318000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>313000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>296000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>304000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>298000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>263000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>265000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>268000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>226000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E22" s="3">
         <v>28000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>32000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>22000</v>
       </c>
       <c r="I22" s="3">
         <v>22000</v>
       </c>
       <c r="J22" s="3">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="K22" s="3">
         <v>24000</v>
       </c>
       <c r="L22" s="3">
+        <v>24000</v>
+      </c>
+      <c r="M22" s="3">
         <v>25000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>21000</v>
       </c>
       <c r="P22" s="3">
         <v>21000</v>
@@ -2138,10 +2177,10 @@
         <v>21000</v>
       </c>
       <c r="S22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="T22" s="3">
         <v>20000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>19000</v>
       </c>
       <c r="U22" s="3">
         <v>19000</v>
@@ -2150,22 +2189,22 @@
         <v>19000</v>
       </c>
       <c r="W22" s="3">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="X22" s="3">
         <v>20000</v>
       </c>
       <c r="Y22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>21000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>18000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>17000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>18000</v>
       </c>
       <c r="AC22" s="3">
         <v>18000</v>
@@ -2174,242 +2213,251 @@
         <v>18000</v>
       </c>
       <c r="AE22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>20000</v>
       </c>
       <c r="AG22" s="3">
         <v>20000</v>
       </c>
       <c r="AH22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>19000</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>20000</v>
       </c>
       <c r="AJ22" s="3">
         <v>20000</v>
       </c>
       <c r="AK22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AL22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E23" s="3">
         <v>367000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>401000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>343000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>374000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>403000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>420000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>132000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>377000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>410000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>455000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>397000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>333000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>319000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>448000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>327000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>273000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>312000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>283000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>219000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>121000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>219000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>231000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>222000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>218000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>248000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>244000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>242000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>227000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>233000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>226000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>193000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>191000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>193000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E24" s="3">
         <v>49000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>50000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>61000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>66000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>55000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-55000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>75000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>87000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>68000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>59000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>63000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>57000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>61000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>20000</v>
       </c>
       <c r="W24" s="3">
         <v>20000</v>
       </c>
       <c r="X24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Y24" s="3">
         <v>22000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>37000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>31000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>36000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-256000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>30000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>22000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>20000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>49000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>18000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>27000</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>25000</v>
       </c>
       <c r="AK24" s="3">
         <v>25000</v>
       </c>
+      <c r="AL24" s="3">
+        <v>25000</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2515,222 +2563,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E26" s="3">
         <v>318000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>351000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>282000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>308000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>348000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>475000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>111000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>302000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>352000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>368000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>329000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>274000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>283000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>442000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>264000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>216000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>288000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>222000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>199000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>101000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>197000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>194000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>191000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>182000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>504000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>214000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>236000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>205000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>213000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>177000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>175000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>164000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>168000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E27" s="3">
         <v>318000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>351000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>282000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>308000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>348000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>475000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>111000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>302000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>352000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>368000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>329000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>274000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>283000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>442000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>264000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>216000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>288000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>222000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>199000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>101000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>197000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>194000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>191000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>182000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>504000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>214000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>236000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>205000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>213000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>177000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>175000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>164000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>168000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2836,8 +2893,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2898,8 +2958,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>10</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
@@ -2916,23 +2976,23 @@
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-19000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-533000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>10</v>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>10</v>
@@ -2940,11 +3000,14 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3050,8 +3113,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3157,8 +3223,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3166,213 +3235,219 @@
         <v>-10000</v>
       </c>
       <c r="E32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>36000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-74000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-3000</v>
       </c>
       <c r="U32" s="3">
         <v>-3000</v>
       </c>
       <c r="V32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="W32" s="3">
         <v>-8000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-39000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E33" s="3">
         <v>318000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>351000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>282000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>308000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>348000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>475000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>111000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>302000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>352000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>368000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>329000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>274000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>283000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>442000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>264000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>216000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>288000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>222000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>199000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>101000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>197000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>194000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>191000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>182000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>504000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>195000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>236000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>205000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-320000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>177000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>175000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>164000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>168000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3478,227 +3553,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E35" s="3">
         <v>318000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>351000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>282000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>308000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>348000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>475000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>111000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>302000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>352000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>368000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>329000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>274000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>283000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>442000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>264000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>216000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>288000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>222000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>199000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>101000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>197000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>194000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>191000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>182000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>504000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>195000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>236000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>205000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-320000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>177000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>175000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>164000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>168000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3736,8 +3820,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3775,115 +3860,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1486000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1467000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1329000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1779000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1671000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1748000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1590000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1329000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1175000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1250000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1053000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1071000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1186000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1113000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1484000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1428000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1380000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1329000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1441000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1358000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1324000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1226000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1382000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1765000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2155000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2057000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2247000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2131000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3011000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2887000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2678000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2389000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3918,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>6000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>45000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>91000</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>10</v>
@@ -3944,8 +4033,8 @@
       <c r="V42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3989,757 +4078,781 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1366000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1328000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1471000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1227000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1249000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1295000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1391000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1339000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1401000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1459000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1405000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1345000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1237000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1205000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1172000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1122000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1075000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1087000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1038000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>930000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>886000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>966000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>930000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>856000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>819000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>833000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>776000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>733000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>754000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>751000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>724000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>678000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>677000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>653000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>991000</v>
+      </c>
+      <c r="E44" s="3">
         <v>997000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>972000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>978000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1000000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1033000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1031000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1072000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1103000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1111000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1038000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1010000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>937000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>879000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>830000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>818000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>791000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>755000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>720000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>746000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>750000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>706000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>679000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>660000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>657000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>653000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>638000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>623000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>594000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>608000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>575000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>566000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>548000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>551000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>533000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E45" s="3">
         <v>315000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>187000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>272000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>283000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>262000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>174000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>290000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>270000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>258000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>282000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>258000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>262000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>232000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>222000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>264000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>268000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>312000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>216000</v>
-      </c>
-      <c r="V45" s="3">
-        <v>211000</v>
       </c>
       <c r="W45" s="3">
         <v>211000</v>
       </c>
       <c r="X45" s="3">
+        <v>211000</v>
+      </c>
+      <c r="Y45" s="3">
         <v>204000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>198000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>176000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>181000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>169000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>187000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>180000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>166000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>151000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>192000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>189000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>186000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>190000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>182000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4208000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4107000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3959000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4256000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4203000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4338000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4186000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4030000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3949000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4078000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3778000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3690000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3643000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3474000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3799000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3632000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3514000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3483000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3415000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3245000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3171000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3102000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3189000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3457000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3812000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3712000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3848000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3667000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4525000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4397000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4169000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3996000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3800000</v>
-      </c>
-      <c r="AJ46" s="3">
-        <v>3635000</v>
       </c>
       <c r="AK46" s="3">
         <v>3635000</v>
       </c>
+      <c r="AL46" s="3">
+        <v>3635000</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E47" s="3">
         <v>173000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>175000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>186000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>177000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>170000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>164000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>190000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>186000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>188000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>195000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>194000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>190000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>191000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>185000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>204000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>188000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>165000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>158000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>148000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>141000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>118000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>102000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>99000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>96000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>77000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>68000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>70000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>139000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>140000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>138000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>137000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>134000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>133000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1988000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1955000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1624000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1533000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1469000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1424000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1377000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1338000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1147000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1250000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1212000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1172000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1144000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1123000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1087000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1070000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1039000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1020000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1029000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1024000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1035000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>850000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>839000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>827000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>829000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>822000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>801000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>798000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>792000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>757000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>716000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>675000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>653000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4969000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4943000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5024000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4357000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4380000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4410000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4435000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4486000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4778000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4793000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4773000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4797000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4854000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4893000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4956000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5008000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5059000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4405000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4433000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4482000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4503000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4648000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4700000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3618000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3650000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3699000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3464000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3448000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2932000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2968000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2987000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2933000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4845,8 +4958,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4952,115 +5068,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E52" s="3">
         <v>703000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>382000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>573000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>563000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>561000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>270000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>592000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>541000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>713000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>536000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>591000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>596000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>625000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>642000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>560000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>567000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>582000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>601000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>642000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>616000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>598000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>611000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>612000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>637000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>635000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>339000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>363000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>390000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>395000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>394000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>425000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>466000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>477000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5166,115 +5288,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12158000</v>
+      </c>
+      <c r="E54" s="3">
         <v>11914000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11846000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10996000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10856000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10948000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10763000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10675000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10792000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10919000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10532000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10484000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10455000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10327000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10705000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10491000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10398000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9674000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9627000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9546000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9455000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9501000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9452000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8625000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9022000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8952000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8541000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8349000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8784000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8698000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8426000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8261000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8016000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7872000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7794000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5312,8 +5440,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5351,650 +5480,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E57" s="3">
         <v>547000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>540000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>497000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>461000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>488000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>418000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>452000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>479000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>540000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>580000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>558000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>503000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>475000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>446000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>416000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>423000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>398000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>354000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>311000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>333000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>329000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>354000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>316000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>314000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>315000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>340000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>273000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>271000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>292000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>305000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>289000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>265000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>268000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E58" s="3">
         <v>16000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>87000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>795000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>420000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>46000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>55000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>238000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>180000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>175000</v>
       </c>
-      <c r="P58" s="3" t="s">
+      <c r="Q58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>130000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>205000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>314000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>75000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>40000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>700000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>675000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>616000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>504000</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
       <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>315000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>345000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>210000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>280000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>190000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>732000</v>
+      </c>
+      <c r="E59" s="3">
         <v>645000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>738000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>608000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>575000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>544000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>610000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>552000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>565000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1158000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1245000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1164000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1135000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1109000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1262000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1178000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1130000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>975000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1038000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>963000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>912000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>888000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1110000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>802000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>804000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>780000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>831000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>741000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>779000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>724000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>748000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>672000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>681000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>631000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>688000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2012000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1869000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1895000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2389000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1958000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1617000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1603000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1760000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1666000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1936000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1861000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1902000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1813000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1584000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1708000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1724000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1758000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1687000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1467000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1314000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1945000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1892000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2080000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1622000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1118000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1095000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1171000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1014000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1361000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1263000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1241000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1187000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1089000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3538000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3524000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3487000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2321000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2306000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2719000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2853000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2912000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2891000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2733000</v>
       </c>
       <c r="M61" s="3">
         <v>2733000</v>
       </c>
       <c r="N61" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="O61" s="3">
         <v>2732000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2730000</v>
       </c>
       <c r="P61" s="3">
         <v>2730000</v>
       </c>
       <c r="Q61" s="3">
+        <v>2730000</v>
+      </c>
+      <c r="R61" s="3">
         <v>2729000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2728000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2727000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2185000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2284000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2283000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1788000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1787000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1791000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1294000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>1798000</v>
       </c>
       <c r="AB61" s="3">
         <v>1798000</v>
       </c>
       <c r="AC61" s="3">
-        <v>1799000</v>
+        <v>1798000</v>
       </c>
       <c r="AD61" s="3">
         <v>1799000</v>
       </c>
       <c r="AE61" s="3">
-        <v>1800000</v>
+        <v>1799000</v>
       </c>
       <c r="AF61" s="3">
         <v>1800000</v>
       </c>
       <c r="AG61" s="3">
-        <v>1801000</v>
+        <v>1800000</v>
       </c>
       <c r="AH61" s="3">
         <v>1801000</v>
       </c>
       <c r="AI61" s="3">
-        <v>1802000</v>
+        <v>1801000</v>
       </c>
       <c r="AJ61" s="3">
         <v>1802000</v>
       </c>
       <c r="AK61" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="AL61" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E62" s="3">
         <v>204000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>194000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>165000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>158000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>210000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>243000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>250000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>641000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>633000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>759000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>790000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>859000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>879000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1093000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1103000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>998000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1003000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>968000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>954000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>974000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>833000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>962000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>981000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1023000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1000000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>968000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1002000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1011000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>527000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>608000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>652000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>681000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6100,8 +6248,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6207,8 +6358,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6314,115 +6468,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6022000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5887000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5948000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5093000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4642000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4760000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4918000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5117000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5011000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5310000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5227000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5393000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5333000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5173000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5316000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5545000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5588000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4870000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4754000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4565000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4687000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4653000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4704000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3878000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3897000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3916000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3974000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3785000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4171000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4176000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3595000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3653000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3644000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3575000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3551000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6460,8 +6620,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6567,8 +6728,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6674,8 +6838,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6781,8 +6948,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6888,115 +7058,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>912000</v>
+      </c>
+      <c r="E72" s="3">
         <v>916000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>750000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>773000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1090000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1061000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>782000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>444000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>700000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>541000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>324000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>139000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>160000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>159000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>348000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>90000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>81000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>130000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>73000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-122000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>178000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>90000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-336000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-416000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-412000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-529000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-126000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-393000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6089000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7102,8 +7278,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7209,8 +7388,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7316,115 +7498,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6136000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6027000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5898000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5903000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6214000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6188000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5845000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5558000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5781000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5609000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5305000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5091000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5122000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5154000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5389000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4946000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4810000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4804000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4873000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4981000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4768000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4848000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4748000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4747000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5125000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5036000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4567000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4564000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4613000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4522000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4831000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4608000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4372000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4297000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4243000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7530,227 +7718,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E81" s="3">
         <v>318000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>351000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>282000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>308000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>348000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>475000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>111000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>302000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>352000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>368000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>329000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>274000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>283000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>442000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>264000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>216000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>288000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>222000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>199000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>101000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>197000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>194000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>191000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>182000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>504000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>195000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>236000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>205000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-320000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>177000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>175000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>164000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>168000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7788,8 +7985,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7797,106 +7995,109 @@
         <v>36000</v>
       </c>
       <c r="E83" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F83" s="3">
         <v>35000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>31000</v>
       </c>
       <c r="I83" s="3">
         <v>31000</v>
       </c>
       <c r="J83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K83" s="3">
         <v>32000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>67000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>73000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>80000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>82000</v>
       </c>
       <c r="P83" s="3">
         <v>82000</v>
       </c>
       <c r="Q83" s="3">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="R83" s="3">
         <v>84000</v>
       </c>
       <c r="S83" s="3">
+        <v>84000</v>
+      </c>
+      <c r="T83" s="3">
         <v>77000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>76000</v>
       </c>
       <c r="U83" s="3">
         <v>76000</v>
       </c>
       <c r="V83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="W83" s="3">
         <v>77000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>76000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>79000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>76000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>55000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>53000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>54000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>56000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>53000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>50000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>51000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>52000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>51000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>54000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>55000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8002,8 +8203,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8109,8 +8313,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8216,8 +8423,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8323,8 +8533,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8430,115 +8643,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E89" s="3">
         <v>431000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>481000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>452000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>333000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>485000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>516000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>562000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>398000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>296000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>448000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>326000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>283000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>255000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>441000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>334000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>472000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>238000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>377000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>290000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>313000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-59000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>314000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>242000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>252000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>213000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>372000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>197000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>303000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>215000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>288000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>228000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>257000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>116000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8576,115 +8795,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-97000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-93000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-92000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-103000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-90000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-84000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-81000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-57000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-76000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-70000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-82000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-64000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-75000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-62000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-55000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-31000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-39000</v>
       </c>
       <c r="AB91" s="3">
         <v>-39000</v>
       </c>
       <c r="AC91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-58000</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-43000</v>
       </c>
       <c r="AI91" s="3">
         <v>-43000</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8790,8 +9013,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8897,115 +9123,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-94000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-954000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-109000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-95000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-89000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-77000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-104000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-110000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-73000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-76000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-59000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-587000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-27000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-32000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-53000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-290000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-473000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-43000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-78000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9043,28 +9275,29 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E96" s="3">
         <v>71000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>68000</v>
       </c>
       <c r="F96" s="3">
         <v>68000</v>
       </c>
       <c r="G96" s="3">
-        <v>69000</v>
+        <v>68000</v>
       </c>
       <c r="H96" s="3">
         <v>69000</v>
       </c>
       <c r="I96" s="3">
-        <v>66000</v>
+        <v>69000</v>
       </c>
       <c r="J96" s="3">
         <v>66000</v>
@@ -9073,22 +9306,22 @@
         <v>66000</v>
       </c>
       <c r="L96" s="3">
+        <v>66000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-67000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-62000</v>
       </c>
       <c r="N96" s="3">
         <v>-62000</v>
       </c>
       <c r="O96" s="3">
-        <v>-63000</v>
+        <v>-62000</v>
       </c>
       <c r="P96" s="3">
         <v>-63000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-59000</v>
+        <v>-63000</v>
       </c>
       <c r="R96" s="3">
         <v>-59000</v>
@@ -9100,34 +9333,34 @@
         <v>-59000</v>
       </c>
       <c r="U96" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-55000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-56000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-55000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-56000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-51000</v>
       </c>
       <c r="Z96" s="3">
         <v>-51000</v>
       </c>
       <c r="AA96" s="3">
-        <v>-52000</v>
+        <v>-51000</v>
       </c>
       <c r="AB96" s="3">
         <v>-52000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-48000</v>
       </c>
       <c r="AE96" s="3">
         <v>-48000</v>
@@ -9136,22 +9369,25 @@
         <v>-48000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9257,8 +9493,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9364,8 +9603,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9471,325 +9713,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-180000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>25000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-246000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-291000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-240000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-201000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-322000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-390000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-341000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-362000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-123000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-546000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-324000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-222000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>166000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-316000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-269000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-231000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-156000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>497000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-582000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-122000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-131000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-589000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>37000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>29000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-56000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E101" s="3">
         <v>7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>22000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-3000</v>
       </c>
       <c r="R101" s="3">
         <v>-3000</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>9000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>8000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y101" s="3">
         <v>-1000</v>
       </c>
       <c r="Z101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>9000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-15000</v>
       </c>
       <c r="AE101" s="3">
         <v>-15000</v>
       </c>
       <c r="AF101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AG101" s="3">
         <v>24000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>18000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>138000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-450000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>108000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-76000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>157000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>261000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>154000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-75000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>197000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-115000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>72000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-374000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>55000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>48000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>51000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-111000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>83000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>35000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>97000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-156000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-383000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-390000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>97000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-190000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>116000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-880000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>124000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>209000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>115000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>174000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>148000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>90000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/A_QTR_FIN.xlsx
@@ -656,493 +656,517 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1861000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1738000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1668000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1681000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1701000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1578000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1573000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1658000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1688000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1672000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1717000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1756000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1849000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1718000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1607000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1674000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1660000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1586000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1525000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1548000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1483000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1238000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1357000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1367000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1274000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1238000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1284000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1294000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1203000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>1206000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>1211000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>1189000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>1114000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>1102000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1111000</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>847000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>871000</v>
+      </c>
+      <c r="F9" s="3">
         <v>850000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>787000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>782000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>785000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>723000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>717000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>750000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>773000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1014000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>793000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>788000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>837000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>779000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>746000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>764000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>760000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>734000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>708000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>710000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>695000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>592000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>583000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>634000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>628000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>581000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>569000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>572000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>576000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>545000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>558000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>538000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>540000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>519000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>511000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>494000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>951000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>990000</v>
+      </c>
+      <c r="F10" s="3">
         <v>888000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>881000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>899000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>916000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>855000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>856000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>908000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>915000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>658000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>924000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>968000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1012000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>939000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>861000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>910000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>900000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>852000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>817000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>838000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>788000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>669000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>655000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>723000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>739000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>693000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>669000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>712000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>718000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>658000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>648000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>673000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>649000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>595000</v>
-      </c>
-      <c r="AK10" s="3">
-        <v>591000</v>
-      </c>
-      <c r="AL10" s="3">
-        <v>573000</v>
       </c>
       <c r="AM10" s="3">
         <v>591000</v>
       </c>
+      <c r="AN10" s="3">
+        <v>573000</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>591000</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1182,121 +1206,129 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>117000</v>
+      </c>
+      <c r="F12" s="3">
         <v>111000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>109000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>113000</v>
       </c>
-      <c r="G12" s="3">
-        <v>131000</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>110000</v>
+      </c>
+      <c r="J12" s="3">
         <v>109000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>113000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>120000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>114000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>118000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>126000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>97000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>119000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>116000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>115000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>117000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>116000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>113000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>109000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>103000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>102000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>92000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>197000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>104000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>102000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>101000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>99000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>102000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>104000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>97000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>92000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>93000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>89000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>87000</v>
-      </c>
-      <c r="AK12" s="3">
-        <v>84000</v>
-      </c>
-      <c r="AL12" s="3">
-        <v>79000</v>
       </c>
       <c r="AM12" s="3">
         <v>84000</v>
       </c>
+      <c r="AN12" s="3">
+        <v>79000</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>84000</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1408,46 +1440,52 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>72000</v>
+      </c>
+      <c r="F14" s="3">
         <v>29000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>108000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-41000</v>
-      </c>
       <c r="H14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>33000</v>
+      </c>
+      <c r="J14" s="3">
         <v>54000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>6000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-273000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>295000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>9000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
@@ -1470,23 +1508,23 @@
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3">
         <v>3000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>3000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>2000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>4000</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
@@ -1494,20 +1532,20 @@
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG14" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>10</v>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>-15000</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>10</v>
@@ -1521,47 +1559,53 @@
       <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AN14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>72000</v>
+        <v>67000</v>
       </c>
       <c r="E15" s="3">
-        <v>73000</v>
+        <v>71000</v>
       </c>
       <c r="F15" s="3">
         <v>72000</v>
       </c>
       <c r="G15" s="3">
+        <v>73000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I15" s="3">
         <v>69000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>63000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>63000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>62000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>62000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>71000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>71000</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1634,8 +1678,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1672,234 +1722,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1387000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1335000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1275000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1291000</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>1290000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1184000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="O17" s="3">
         <v>1326000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="P17" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1378000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>1247000</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1298000</v>
+      </c>
+      <c r="U17" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="V17" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="W17" s="3">
+        <v>1237000</v>
+      </c>
+      <c r="X17" s="3">
+        <v>1220000</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1184000</v>
       </c>
-      <c r="I17" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1259000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1534000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1240000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1326000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1330000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1378000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1307000</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1247000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>1298000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1265000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1250000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1237000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1220000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1184000</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1031000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1136000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1142000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1117000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1049000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1022000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1034000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1035000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>982000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>996000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>972000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>956000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>913000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>901000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>861000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>928000</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>505000</v>
+      </c>
+      <c r="F18" s="3">
         <v>403000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>393000</v>
       </c>
-      <c r="F18" s="3">
-        <v>390000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>375000</v>
-      </c>
       <c r="H18" s="3">
+        <v>391000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>436000</v>
+      </c>
+      <c r="J18" s="3">
         <v>394000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>373000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>399000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>154000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>432000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>391000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>426000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>471000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>411000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>360000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>376000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>395000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>336000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>288000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>328000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>299000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>230000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>102000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>215000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>250000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>225000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>216000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>250000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>259000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>221000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>210000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>239000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>233000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>201000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>201000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>206000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1939,281 +2003,295 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>74000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>24000</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>36000</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AM20" s="3">
         <v>10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="AN20" s="3">
         <v>7000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>9000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>7000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-36000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>74000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>12000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>39000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>24000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>15000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>19000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>16000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>39000</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>36000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>14000</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>13000</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>7000</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>481000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>595000</v>
+      </c>
+      <c r="F21" s="3">
         <v>479000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>456000</v>
       </c>
-      <c r="F21" s="3">
-        <v>452000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>437000</v>
-      </c>
       <c r="H21" s="3">
+        <v>467000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>511000</v>
+      </c>
+      <c r="J21" s="3">
         <v>463000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>439000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>475000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>214000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>509000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>469000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>502000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>551000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>496000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>436000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>422000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>553000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>432000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>370000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>407000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>378000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>315000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>217000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>318000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>328000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>295000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>288000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>320000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>318000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>313000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>296000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>304000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>298000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>263000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>265000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>268000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>226000</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="E22" s="3">
-        <v>29000</v>
+        <v>27000</v>
       </c>
       <c r="F22" s="3">
         <v>28000</v>
       </c>
       <c r="G22" s="3">
+        <v>29000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I22" s="3">
         <v>32000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>22000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>20000</v>
       </c>
       <c r="J22" s="3">
         <v>22000</v>
       </c>
       <c r="K22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L22" s="3">
         <v>22000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="N22" s="3">
         <v>24000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>24000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>25000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>23000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>19000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>21000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>21000</v>
       </c>
       <c r="S22" s="3">
         <v>21000</v>
@@ -2222,290 +2300,308 @@
         <v>21000</v>
       </c>
       <c r="U22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="V22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="W22" s="3">
         <v>20000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>19000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>19000</v>
       </c>
       <c r="X22" s="3">
         <v>19000</v>
       </c>
       <c r="Y22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>20000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>20000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>21000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>18000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>17000</v>
       </c>
       <c r="AD22" s="3">
         <v>18000</v>
       </c>
       <c r="AE22" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="AF22" s="3">
         <v>18000</v>
       </c>
       <c r="AG22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>19000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>20000</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>20000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>19000</v>
       </c>
       <c r="AK22" s="3">
         <v>20000</v>
       </c>
       <c r="AL22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AM22" s="3">
         <v>20000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AO22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>442000</v>
+      </c>
+      <c r="F23" s="3">
         <v>366000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>260000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>367000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>401000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>343000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>374000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>403000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>420000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>132000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>377000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>410000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>455000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>397000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>333000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>319000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>448000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>327000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>273000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>312000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>283000</v>
-      </c>
-      <c r="X23" s="3">
-        <v>219000</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>121000</v>
       </c>
       <c r="Z23" s="3">
         <v>219000</v>
       </c>
       <c r="AA23" s="3">
+        <v>121000</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>219000</v>
+      </c>
+      <c r="AC23" s="3">
         <v>231000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>222000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>218000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>248000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>244000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>242000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>227000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>233000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>226000</v>
-      </c>
-      <c r="AJ23" s="3">
-        <v>193000</v>
-      </c>
-      <c r="AK23" s="3">
-        <v>191000</v>
       </c>
       <c r="AL23" s="3">
         <v>193000</v>
       </c>
       <c r="AM23" s="3">
+        <v>191000</v>
+      </c>
+      <c r="AN23" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AO23" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F24" s="3">
         <v>30000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>45000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>49000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>50000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>61000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>66000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>55000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-55000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>21000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>75000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>58000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>87000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>68000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>59000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>36000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>6000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>63000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>57000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>24000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>61000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>20000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>20000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>22000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>37000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>31000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>36000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-256000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>30000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>6000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>22000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>20000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>49000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>18000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>27000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>25000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2617,234 +2713,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>434000</v>
+      </c>
+      <c r="F26" s="3">
         <v>336000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>215000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>318000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>351000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>282000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>308000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>348000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>475000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>111000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>302000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>352000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>368000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>329000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>274000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>283000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>442000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>264000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>216000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>288000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>222000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>199000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>101000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>197000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>194000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>191000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>182000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>504000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>214000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>236000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>205000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>213000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>175000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>164000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>168000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>434000</v>
+      </c>
+      <c r="F27" s="3">
         <v>336000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>215000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>318000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>351000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>282000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>308000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>348000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>475000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>111000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>302000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>352000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>368000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>329000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>274000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>283000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>442000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>264000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>216000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>288000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>222000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>199000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>101000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>197000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>194000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>191000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>182000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>504000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>214000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>236000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>205000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>213000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>175000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>164000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>168000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2956,8 +3070,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3024,11 +3144,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
@@ -3042,35 +3162,41 @@
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
-        <v>-19000</v>
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AG29" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="AH29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-533000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>10</v>
+      <c r="AK29" s="3">
+        <v>0</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AM29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3182,8 +3308,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3295,234 +3427,252 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>36000</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="AN32" s="3">
         <v>-7000</v>
       </c>
-      <c r="H32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>14000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>7000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>36000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-74000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-36000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="AL32" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>434000</v>
+      </c>
+      <c r="F33" s="3">
         <v>336000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>215000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>318000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>351000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>282000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>308000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>348000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>475000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>111000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>302000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>352000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>368000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>329000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>274000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>283000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>442000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>264000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>216000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>288000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>222000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>199000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>101000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>197000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>194000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>191000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>182000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>504000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>195000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>236000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>205000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-320000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>175000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>164000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>168000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3634,239 +3784,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>434000</v>
+      </c>
+      <c r="F35" s="3">
         <v>336000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>215000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>318000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>351000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>282000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>308000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>348000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>475000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>111000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>302000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>352000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>368000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>329000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>274000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>283000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>442000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>264000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>216000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>288000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>222000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>199000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>101000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>197000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>194000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>191000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>182000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>504000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>195000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>236000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>205000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-320000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>175000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>164000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>168000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3906,8 +4074,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3947,121 +4117,129 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1758000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1789000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1535000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1486000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1467000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1329000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1779000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1671000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1748000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1590000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1329000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1175000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1250000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1053000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1071000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1186000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1113000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1484000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1428000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1380000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1329000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1441000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1358000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1324000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1226000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1382000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1765000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2155000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2057000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2247000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2131000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>3011000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2887000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2678000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>2389000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4102,22 +4280,22 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>6000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>21000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>45000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>91000</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>10</v>
@@ -4128,11 +4306,11 @@
       <c r="X42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -4173,799 +4351,847 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1595000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1382000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1366000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1328000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1471000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1227000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1249000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1295000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1391000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1339000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1401000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1459000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1405000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1345000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1237000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1205000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1172000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1122000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1075000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1087000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1038000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>930000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>886000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>966000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>930000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>856000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>819000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>833000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>776000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>733000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>754000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>751000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>724000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>678000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>677000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>653000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>631000</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1059000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1014000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>991000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>997000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>972000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>978000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1000000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1033000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1031000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1072000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1103000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1111000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1038000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1010000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>937000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>879000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>830000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>818000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>791000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>755000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>720000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>746000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>750000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>706000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>679000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>660000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>657000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>653000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>638000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>623000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>594000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>608000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>575000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>566000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>548000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>551000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>533000</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>185000</v>
+      </c>
+      <c r="F45" s="3">
         <v>322000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>365000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>315000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>187000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>272000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>283000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>262000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>174000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>290000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>270000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>258000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>282000</v>
       </c>
       <c r="P45" s="3">
         <v>258000</v>
       </c>
       <c r="Q45" s="3">
+        <v>282000</v>
+      </c>
+      <c r="R45" s="3">
+        <v>258000</v>
+      </c>
+      <c r="S45" s="3">
         <v>262000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>232000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>222000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>264000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>268000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>312000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>216000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>211000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>211000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>204000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>198000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>176000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>181000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>169000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>187000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>180000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>166000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>151000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>192000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>189000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>186000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>190000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>182000</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4615000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4594000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4253000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4208000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4107000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3959000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4256000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4203000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4338000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4186000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4030000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3949000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4078000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3778000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3690000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3643000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3474000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3799000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3632000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3514000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3483000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3415000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3245000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3171000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3102000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3189000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3457000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3812000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3712000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3848000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3667000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>4525000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>4397000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>4169000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>3996000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>3800000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>3635000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>3635000</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E47" s="3">
         <v>133000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
+        <v>133000</v>
+      </c>
+      <c r="G47" s="3">
         <v>135000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>173000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>175000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>186000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>177000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>170000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>164000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>190000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>186000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>188000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>195000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>194000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>190000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>191000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>185000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>204000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>188000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>165000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>158000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>148000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>141000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>118000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>102000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>99000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>96000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>77000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>68000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>70000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>139000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>140000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>138000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>137000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>134000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>133000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2267000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2206000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2145000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2094000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1988000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1955000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1624000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1533000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1469000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1424000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1377000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1338000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1147000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1250000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1212000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1172000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1144000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1123000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1087000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1070000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1039000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1020000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1029000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1024000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1035000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>850000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>839000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>827000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>829000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>822000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>801000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>798000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>792000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>757000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>716000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>675000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>653000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4910000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4944000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4969000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4943000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>5024000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4357000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4380000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4410000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4435000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4486000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4778000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4793000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4773000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4797000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4854000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>4893000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4956000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>5008000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5059000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>4405000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4433000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4482000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4503000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4648000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4700000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>3618000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3650000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>3699000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>3464000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>3448000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>2932000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>2968000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>2987000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>2974000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>2933000</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5077,8 +5303,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5190,121 +5422,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>886000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>449000</v>
+      </c>
+      <c r="F52" s="3">
         <v>751000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>752000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>703000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>382000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>573000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>563000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>561000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>270000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>592000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>541000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>713000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>536000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>591000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>596000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>625000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>642000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>560000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>567000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>582000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>601000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>642000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>616000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>598000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>611000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>612000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>637000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>635000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>339000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>363000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>390000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>395000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>394000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>425000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>466000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>477000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5416,121 +5660,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12813000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12727000</v>
+      </c>
+      <c r="F54" s="3">
         <v>12226000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>12158000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11914000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11846000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10996000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10856000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10948000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10763000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10675000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10792000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>10919000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10532000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>10484000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>10455000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>10327000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>10705000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>10491000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>10398000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>9674000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>9627000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>9546000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>9455000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>9501000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>9452000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>8625000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>9022000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>8952000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>8541000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>8349000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>8784000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>8698000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>8426000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>8261000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>8016000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>7872000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>7794000</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5570,8 +5826,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5611,686 +5869,724 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>602000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>570000</v>
+      </c>
+      <c r="F57" s="3">
         <v>530000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>517000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>547000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>540000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>497000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>461000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>488000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>418000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>452000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>479000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>540000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>580000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>558000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>503000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>475000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>446000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>416000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>423000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>398000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>354000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>311000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>333000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>329000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>354000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>316000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>314000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>315000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>340000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>273000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>271000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>292000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>305000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>289000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>265000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>268000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>348000</v>
+      </c>
+      <c r="F58" s="3">
         <v>59000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>146000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>16000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>87000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>795000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>420000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>46000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>55000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>238000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>36000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>180000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>175000</v>
       </c>
-      <c r="R58" s="3" t="s">
+      <c r="T58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>130000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>205000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>314000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>75000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>40000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>700000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>675000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>616000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>504000</v>
       </c>
-      <c r="AC58" s="3" t="s">
+      <c r="AE58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD58" s="3" t="s">
+      <c r="AF58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>0</v>
-      </c>
       <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
         <v>315000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>345000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>210000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>280000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>241000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>190000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>740000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>823000</v>
+      </c>
+      <c r="F59" s="3">
         <v>687000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>732000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>645000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>738000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>608000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>575000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>544000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>610000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>552000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>565000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1158000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1245000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1164000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1135000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1109000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1262000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1178000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1130000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>975000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1038000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>963000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>912000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>888000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1110000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>802000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>804000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>780000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>831000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>741000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>779000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>724000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>748000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>672000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>681000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>631000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>688000</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2234000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2347000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1892000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2012000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1869000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1895000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2389000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1958000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1617000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1603000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1760000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1666000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1936000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1861000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1902000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1813000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1584000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1708000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1724000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1758000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1687000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1467000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1314000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1945000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1892000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2080000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1622000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1118000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1095000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1171000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1014000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>1361000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>1263000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>1241000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>1187000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>1089000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3246000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3195000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3535000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3538000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3524000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3487000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2321000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2306000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2719000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2853000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2912000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2891000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2733000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2733000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2732000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2730000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2730000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2729000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2728000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2727000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2185000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2284000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2283000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1788000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1787000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1791000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1294000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1798000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1798000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1799000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1799000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1800000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1800000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1801000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>1801000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>1802000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>1802000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>92000</v>
+      </c>
+      <c r="F62" s="3">
         <v>130000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>164000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>204000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>194000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>165000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>158000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>200000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>210000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>243000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>250000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>641000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>633000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>759000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>790000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>859000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>879000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1093000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1103000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>998000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1003000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>968000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>954000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>974000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>833000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>962000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>981000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1023000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1000000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>968000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1002000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1011000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>527000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>608000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>652000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>681000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6402,8 +6698,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6515,8 +6817,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6628,121 +6936,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5905000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5986000</v>
+      </c>
+      <c r="F66" s="3">
         <v>5856000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6022000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5887000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5948000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5093000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4642000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4760000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4918000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5117000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5011000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5310000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5227000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5393000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5333000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5173000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5316000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5545000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5588000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4870000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4754000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>4565000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4687000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>4653000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>4704000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>3878000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>3897000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>3916000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>3974000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>3785000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>4171000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>4176000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>3595000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>3653000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>3644000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>3575000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>3551000</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6782,8 +7102,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6895,8 +7217,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7008,8 +7336,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7121,8 +7455,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7234,121 +7574,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1389000</v>
+      </c>
+      <c r="F72" s="3">
         <v>1102000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>912000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>916000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>750000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>773000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1090000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1061000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>782000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>444000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>700000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>541000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>324000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>139000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>160000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>159000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>348000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>90000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-12000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>4000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>81000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>130000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>15000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>73000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-122000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>178000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>90000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-336000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-416000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-412000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-529000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-126000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-393000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>6089000</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7460,8 +7812,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7573,8 +7931,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7686,121 +8050,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6908000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6741000</v>
+      </c>
+      <c r="F76" s="3">
         <v>6370000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6136000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6027000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5898000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5903000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6214000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6188000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5845000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5558000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5781000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5609000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5305000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5091000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5122000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5154000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5389000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4946000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4810000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4804000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4873000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4981000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4768000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4848000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4748000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4747000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5125000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5036000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4567000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>4564000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>4613000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>4522000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>4831000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>4608000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>4372000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>4297000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>4243000</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7912,239 +8288,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>434000</v>
+      </c>
+      <c r="F81" s="3">
         <v>336000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>215000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>318000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>351000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>282000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>308000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>348000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>475000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>111000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>302000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>352000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>368000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>329000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>274000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>283000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>442000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>264000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>216000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>288000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>222000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>199000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>101000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>197000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>194000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>191000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>182000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>504000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>195000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>236000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>205000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-320000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>175000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>164000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>168000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8184,121 +8578,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>42000</v>
+      </c>
+      <c r="F83" s="3">
         <v>38000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>36000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>36000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>35000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>32000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>33000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>31000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>31000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>32000</v>
       </c>
       <c r="M83" s="3">
         <v>31000</v>
       </c>
       <c r="N83" s="3">
+        <v>32000</v>
+      </c>
+      <c r="O83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="P83" s="3">
         <v>67000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>73000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>80000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>82000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>82000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>84000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>84000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>77000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>76000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>76000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>77000</v>
       </c>
       <c r="Y83" s="3">
         <v>76000</v>
       </c>
       <c r="Z83" s="3">
-        <v>79000</v>
+        <v>77000</v>
       </c>
       <c r="AA83" s="3">
         <v>76000</v>
       </c>
       <c r="AB83" s="3">
+        <v>79000</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="AD83" s="3">
         <v>55000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>53000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>54000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>56000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>53000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>50000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>51000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>52000</v>
       </c>
       <c r="AJ83" s="3">
         <v>51000</v>
       </c>
       <c r="AK83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>51000</v>
+      </c>
+      <c r="AM83" s="3">
         <v>54000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>55000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8410,8 +8812,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8523,8 +8931,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8636,8 +9050,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8749,8 +9169,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8862,121 +9288,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>545000</v>
+      </c>
+      <c r="F89" s="3">
         <v>362000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>221000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>431000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>481000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>452000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>333000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>485000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>516000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>562000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>398000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>296000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>448000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>326000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>283000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>255000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>441000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>334000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>472000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>238000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>377000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>290000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>313000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>314000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>242000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>252000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>213000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>372000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>197000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>303000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>215000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>288000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>228000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>257000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>116000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9016,121 +9454,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-103000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-114000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-97000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-93000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-92000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-103000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-90000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-84000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-81000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-57000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-76000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-70000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-82000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-64000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-75000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-62000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-55000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-31000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-41000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-27000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-33000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9242,8 +9688,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9355,121 +9807,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-96000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-114000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-94000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-954000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-100000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-109000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-95000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-40000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-89000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-77000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-104000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-110000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-76000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-79000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-59000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-61000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-587000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-42000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-27000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-51000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-473000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-60000</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-101000</v>
-      </c>
-      <c r="AK94" s="3">
-        <v>-43000</v>
       </c>
       <c r="AL94" s="3">
         <v>-101000</v>
       </c>
       <c r="AM94" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AN94" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-78000</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9509,13 +9973,15 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>71000</v>
+        <v>72000</v>
       </c>
       <c r="E96" s="3">
         <v>70000</v>
@@ -9524,46 +9990,46 @@
         <v>71000</v>
       </c>
       <c r="G96" s="3">
+        <v>70000</v>
+      </c>
+      <c r="H96" s="3">
+        <v>71000</v>
+      </c>
+      <c r="I96" s="3">
         <v>68000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>68000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>69000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>69000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>66000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>66000</v>
       </c>
       <c r="M96" s="3">
         <v>66000</v>
       </c>
       <c r="N96" s="3">
+        <v>66000</v>
+      </c>
+      <c r="O96" s="3">
+        <v>66000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-67000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-62000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-63000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-63000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-59000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-59000</v>
       </c>
       <c r="U96" s="3">
         <v>-59000</v>
@@ -9572,10 +10038,10 @@
         <v>-59000</v>
       </c>
       <c r="W96" s="3">
-        <v>-55000</v>
+        <v>-59000</v>
       </c>
       <c r="X96" s="3">
-        <v>-56000</v>
+        <v>-59000</v>
       </c>
       <c r="Y96" s="3">
         <v>-55000</v>
@@ -9584,34 +10050,34 @@
         <v>-56000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-51000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-51000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-52000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-48000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-48000</v>
       </c>
       <c r="AH96" s="3">
         <v>-48000</v>
       </c>
       <c r="AI96" s="3">
-        <v>-43000</v>
+        <v>-48000</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-42000</v>
+        <v>-48000</v>
       </c>
       <c r="AK96" s="3">
         <v>-43000</v>
@@ -9620,10 +10086,16 @@
         <v>-42000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9735,8 +10207,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9848,8 +10326,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9961,343 +10445,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-222000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-219000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-116000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-180000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>25000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-246000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-291000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-240000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-201000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-322000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-390000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-17000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-341000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-362000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-123000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-546000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-324000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-222000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>166000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-316000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-269000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-231000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-156000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>497000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-582000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-122000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-131000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-589000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>37000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>29000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-56000</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>7000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-14000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>22000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-12000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>22000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-14000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-12000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-3000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>9000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>9000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>24000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>18000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>254000</v>
+      </c>
+      <c r="F102" s="3">
         <v>48000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>19000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>138000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-450000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>108000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-76000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>157000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>261000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>154000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-75000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>197000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-17000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>72000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-374000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>55000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>48000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>51000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-111000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>83000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>35000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>97000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-156000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-383000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-390000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>97000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-190000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>116000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-880000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>124000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>209000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>115000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>174000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>148000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>90000</v>
       </c>
     </row>
